--- a/thaco/Archive/BANG LUONG MAU 1.xlsx
+++ b/thaco/Archive/BANG LUONG MAU 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/Archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F48E024-303D-694D-8EB7-1C3CB360C604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FE0BF3-5E52-DD46-96E4-C08A3C2AB999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" activeTab="1" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
+    <workbookView xWindow="39600" yWindow="780" windowWidth="36740" windowHeight="14780" tabRatio="761" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4292,16 +4292,71 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    TV: Thử việc
-CT: Chính thức</t>
+          <t xml:space="preserve">[Threaded comment]
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    TV: Thử việc
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>CT: Chính thức</t>
         </r>
       </text>
     </comment>
@@ -4310,18 +4365,91 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Đối tượng Lương ngày tại các TĐTV
-Reply:
-    LT: Lương Tháng
-LN: Lương ngày
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    Đối tượng Lương ngày tại các TĐTV
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Reply:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    LT: Lương Tháng
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">LN: Lương ngày
 </t>
         </r>
       </text>
@@ -4342,16 +4470,71 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    TV: Thử việc
-CT: Chính thức</t>
+          <t xml:space="preserve">[Threaded comment]
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    TV: Thử việc
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>CT: Chính thức</t>
         </r>
       </text>
     </comment>
@@ -5256,22 +5439,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="7.5"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -5586,7 +5770,7 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="470">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6243,11 +6427,98 @@
     <xf numFmtId="43" fontId="22" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6258,21 +6529,6 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6318,15 +6574,6 @@
     <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="22" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6336,12 +6583,6 @@
     <xf numFmtId="165" fontId="22" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6351,146 +6592,11 @@
     <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6501,6 +6607,24 @@
     <xf numFmtId="165" fontId="22" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6522,26 +6646,23 @@
     <xf numFmtId="43" fontId="22" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6552,50 +6673,449 @@
     <xf numFmtId="165" fontId="23" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7398,101 +7918,101 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="316" t="str">
+      <c r="A3" s="251" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
-        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2025</v>
-      </c>
-      <c r="B3" s="316"/>
-      <c r="C3" s="316"/>
-      <c r="D3" s="316"/>
-      <c r="E3" s="316"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="316"/>
-      <c r="K3" s="316"/>
-      <c r="L3" s="316"/>
-      <c r="M3" s="316"/>
-      <c r="N3" s="316"/>
-      <c r="O3" s="316"/>
-      <c r="P3" s="316"/>
-      <c r="Q3" s="316"/>
-      <c r="R3" s="316"/>
-      <c r="S3" s="316"/>
-      <c r="T3" s="316"/>
-      <c r="U3" s="316"/>
-      <c r="V3" s="316"/>
-      <c r="W3" s="316"/>
-      <c r="X3" s="316"/>
-      <c r="Y3" s="316"/>
-      <c r="Z3" s="316"/>
-      <c r="AA3" s="316"/>
-      <c r="AB3" s="316"/>
-      <c r="AC3" s="316"/>
-      <c r="AD3" s="316"/>
-      <c r="AE3" s="316"/>
-      <c r="AF3" s="316"/>
-      <c r="AG3" s="316"/>
-      <c r="AH3" s="316"/>
-      <c r="AI3" s="316"/>
-      <c r="AJ3" s="316"/>
-      <c r="AK3" s="316"/>
-      <c r="AL3" s="316"/>
-      <c r="AM3" s="316"/>
-      <c r="AN3" s="316"/>
-      <c r="AO3" s="316"/>
-      <c r="AP3" s="316"/>
-      <c r="AQ3" s="316"/>
-      <c r="AR3" s="316"/>
-      <c r="AS3" s="316"/>
-      <c r="AT3" s="316"/>
-      <c r="AU3" s="316"/>
-      <c r="AV3" s="316"/>
-      <c r="AW3" s="316"/>
-      <c r="AX3" s="316"/>
-      <c r="AY3" s="316"/>
-      <c r="AZ3" s="316"/>
-      <c r="BA3" s="316"/>
-      <c r="BB3" s="316"/>
-      <c r="BC3" s="316"/>
-      <c r="BD3" s="316"/>
-      <c r="BE3" s="316"/>
-      <c r="BF3" s="316"/>
-      <c r="BG3" s="316"/>
-      <c r="BH3" s="316"/>
-      <c r="BI3" s="316"/>
-      <c r="BJ3" s="316"/>
-      <c r="BK3" s="316"/>
-      <c r="BL3" s="316"/>
-      <c r="BM3" s="316"/>
-      <c r="BN3" s="316"/>
-      <c r="BO3" s="316"/>
-      <c r="BP3" s="316"/>
-      <c r="BQ3" s="316"/>
-      <c r="BR3" s="316"/>
-      <c r="BS3" s="316"/>
-      <c r="BT3" s="316"/>
-      <c r="BU3" s="316"/>
+        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
+      </c>
+      <c r="B3" s="251"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="251"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
+      <c r="M3" s="251"/>
+      <c r="N3" s="251"/>
+      <c r="O3" s="251"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
+      <c r="AA3" s="251"/>
+      <c r="AB3" s="251"/>
+      <c r="AC3" s="251"/>
+      <c r="AD3" s="251"/>
+      <c r="AE3" s="251"/>
+      <c r="AF3" s="251"/>
+      <c r="AG3" s="251"/>
+      <c r="AH3" s="251"/>
+      <c r="AI3" s="251"/>
+      <c r="AJ3" s="251"/>
+      <c r="AK3" s="251"/>
+      <c r="AL3" s="251"/>
+      <c r="AM3" s="251"/>
+      <c r="AN3" s="251"/>
+      <c r="AO3" s="251"/>
+      <c r="AP3" s="251"/>
+      <c r="AQ3" s="251"/>
+      <c r="AR3" s="251"/>
+      <c r="AS3" s="251"/>
+      <c r="AT3" s="251"/>
+      <c r="AU3" s="251"/>
+      <c r="AV3" s="251"/>
+      <c r="AW3" s="251"/>
+      <c r="AX3" s="251"/>
+      <c r="AY3" s="251"/>
+      <c r="AZ3" s="251"/>
+      <c r="BA3" s="251"/>
+      <c r="BB3" s="251"/>
+      <c r="BC3" s="251"/>
+      <c r="BD3" s="251"/>
+      <c r="BE3" s="251"/>
+      <c r="BF3" s="251"/>
+      <c r="BG3" s="251"/>
+      <c r="BH3" s="251"/>
+      <c r="BI3" s="251"/>
+      <c r="BJ3" s="251"/>
+      <c r="BK3" s="251"/>
+      <c r="BL3" s="251"/>
+      <c r="BM3" s="251"/>
+      <c r="BN3" s="251"/>
+      <c r="BO3" s="251"/>
+      <c r="BP3" s="251"/>
+      <c r="BQ3" s="251"/>
+      <c r="BR3" s="251"/>
+      <c r="BS3" s="251"/>
+      <c r="BT3" s="251"/>
+      <c r="BU3" s="251"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="297" t="s">
+      <c r="BW3" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="297"/>
-      <c r="BY3" s="297"/>
-      <c r="BZ3" s="297"/>
-      <c r="CA3" s="297"/>
-      <c r="CB3" s="298"/>
+      <c r="BX3" s="261"/>
+      <c r="BY3" s="261"/>
+      <c r="BZ3" s="261"/>
+      <c r="CA3" s="261"/>
+      <c r="CB3" s="262"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
-      <c r="CE3" s="240" t="s">
+      <c r="CE3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="CF3" s="241">
+      <c r="CF3" s="325">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:87" s="16" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="4" spans="1:87" s="16" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -7566,16 +8086,16 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="298"/>
-      <c r="BX4" s="298"/>
-      <c r="BY4" s="298"/>
-      <c r="BZ4" s="298"/>
-      <c r="CA4" s="298"/>
-      <c r="CB4" s="298"/>
+      <c r="BW4" s="262"/>
+      <c r="BX4" s="262"/>
+      <c r="BY4" s="262"/>
+      <c r="BZ4" s="262"/>
+      <c r="CA4" s="262"/>
+      <c r="CB4" s="262"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
-    <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -7649,16 +8169,16 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="298"/>
-      <c r="BX5" s="298"/>
-      <c r="BY5" s="298"/>
-      <c r="BZ5" s="298"/>
-      <c r="CA5" s="298"/>
-      <c r="CB5" s="298"/>
+      <c r="BW5" s="262"/>
+      <c r="BX5" s="262"/>
+      <c r="BY5" s="262"/>
+      <c r="BZ5" s="262"/>
+      <c r="CA5" s="262"/>
+      <c r="CB5" s="262"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
-    <row r="6" spans="1:87" s="14" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="6" spans="1:87" s="14" customFormat="1" ht="18.75" customHeight="1" outlineLevel="1">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -7732,16 +8252,16 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="297"/>
-      <c r="BX6" s="297"/>
-      <c r="BY6" s="297"/>
-      <c r="BZ6" s="297"/>
-      <c r="CA6" s="297"/>
-      <c r="CB6" s="298"/>
+      <c r="BW6" s="261"/>
+      <c r="BX6" s="261"/>
+      <c r="BY6" s="261"/>
+      <c r="BZ6" s="261"/>
+      <c r="CA6" s="261"/>
+      <c r="CB6" s="262"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
-    <row r="7" spans="1:87" s="14" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="7" spans="1:87" s="14" customFormat="1" ht="12.75" customHeight="1" outlineLevel="1">
       <c r="A7" s="21"/>
       <c r="B7" s="22"/>
       <c r="C7" s="21"/>
@@ -7824,357 +8344,357 @@
       <c r="CC7" s="25"/>
       <c r="CD7" s="25"/>
     </row>
-    <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="299" t="s">
+    <row r="8" spans="1:87" s="11" customFormat="1" ht="31" customHeight="1">
+      <c r="A8" s="447" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="302" t="s">
+      <c r="B8" s="450" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="245" t="s">
+      <c r="C8" s="398" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="305" t="s">
+      <c r="D8" s="453" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="305" t="s">
+      <c r="E8" s="453" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="245" t="s">
+      <c r="F8" s="398" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="308" t="s">
+      <c r="G8" s="456" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="276" t="s">
+      <c r="H8" s="426" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="276" t="s">
+      <c r="I8" s="426" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="308" t="s">
+      <c r="J8" s="456" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="279" t="s">
+      <c r="K8" s="429" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="280"/>
-      <c r="P8" s="280"/>
-      <c r="Q8" s="280"/>
-      <c r="R8" s="280"/>
-      <c r="S8" s="280"/>
-      <c r="T8" s="280"/>
-      <c r="U8" s="280"/>
-      <c r="V8" s="280"/>
-      <c r="W8" s="280"/>
-      <c r="X8" s="280"/>
-      <c r="Y8" s="281" t="s">
+      <c r="L8" s="430"/>
+      <c r="M8" s="430"/>
+      <c r="N8" s="430"/>
+      <c r="O8" s="430"/>
+      <c r="P8" s="430"/>
+      <c r="Q8" s="430"/>
+      <c r="R8" s="430"/>
+      <c r="S8" s="430"/>
+      <c r="T8" s="430"/>
+      <c r="U8" s="430"/>
+      <c r="V8" s="430"/>
+      <c r="W8" s="430"/>
+      <c r="X8" s="430"/>
+      <c r="Y8" s="431" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="282"/>
-      <c r="AA8" s="282"/>
-      <c r="AB8" s="282"/>
-      <c r="AC8" s="282"/>
-      <c r="AD8" s="282"/>
-      <c r="AE8" s="282"/>
-      <c r="AF8" s="282"/>
-      <c r="AG8" s="282"/>
-      <c r="AH8" s="282"/>
-      <c r="AI8" s="282"/>
-      <c r="AJ8" s="282"/>
-      <c r="AK8" s="282"/>
-      <c r="AL8" s="282"/>
-      <c r="AM8" s="282"/>
-      <c r="AN8" s="282"/>
-      <c r="AO8" s="283"/>
-      <c r="AP8" s="308" t="s">
+      <c r="Z8" s="432"/>
+      <c r="AA8" s="432"/>
+      <c r="AB8" s="432"/>
+      <c r="AC8" s="432"/>
+      <c r="AD8" s="432"/>
+      <c r="AE8" s="432"/>
+      <c r="AF8" s="432"/>
+      <c r="AG8" s="432"/>
+      <c r="AH8" s="432"/>
+      <c r="AI8" s="432"/>
+      <c r="AJ8" s="432"/>
+      <c r="AK8" s="432"/>
+      <c r="AL8" s="432"/>
+      <c r="AM8" s="432"/>
+      <c r="AN8" s="432"/>
+      <c r="AO8" s="433"/>
+      <c r="AP8" s="456" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="308" t="s">
+      <c r="AQ8" s="456" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="308" t="s">
+      <c r="AR8" s="456" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="308" t="s">
+      <c r="AS8" s="456" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="308" t="s">
+      <c r="AT8" s="456" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="308" t="s">
+      <c r="AU8" s="456" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="245" t="s">
+      <c r="AV8" s="398" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="245" t="s">
+      <c r="AW8" s="398" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="245" t="s">
+      <c r="AX8" s="398" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="313" t="s">
+      <c r="AY8" s="461" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="314"/>
-      <c r="BA8" s="314"/>
-      <c r="BB8" s="314"/>
-      <c r="BC8" s="314"/>
-      <c r="BD8" s="314"/>
-      <c r="BE8" s="314"/>
-      <c r="BF8" s="314"/>
-      <c r="BG8" s="314"/>
-      <c r="BH8" s="314"/>
-      <c r="BI8" s="314"/>
-      <c r="BJ8" s="314"/>
-      <c r="BK8" s="314"/>
-      <c r="BL8" s="314"/>
-      <c r="BM8" s="314"/>
-      <c r="BN8" s="314"/>
-      <c r="BO8" s="314"/>
-      <c r="BP8" s="314"/>
-      <c r="BQ8" s="315"/>
-      <c r="BR8" s="268" t="s">
+      <c r="AZ8" s="462"/>
+      <c r="BA8" s="462"/>
+      <c r="BB8" s="462"/>
+      <c r="BC8" s="462"/>
+      <c r="BD8" s="462"/>
+      <c r="BE8" s="462"/>
+      <c r="BF8" s="462"/>
+      <c r="BG8" s="462"/>
+      <c r="BH8" s="462"/>
+      <c r="BI8" s="462"/>
+      <c r="BJ8" s="462"/>
+      <c r="BK8" s="462"/>
+      <c r="BL8" s="462"/>
+      <c r="BM8" s="462"/>
+      <c r="BN8" s="462"/>
+      <c r="BO8" s="462"/>
+      <c r="BP8" s="462"/>
+      <c r="BQ8" s="463"/>
+      <c r="BR8" s="418" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="275"/>
-      <c r="BT8" s="265" t="s">
+      <c r="BS8" s="425"/>
+      <c r="BT8" s="415" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="268" t="s">
+      <c r="BU8" s="418" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="250" t="s">
+      <c r="BW8" s="403" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="253" t="s">
+      <c r="BX8" s="406" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="254"/>
-      <c r="BZ8" s="254"/>
-      <c r="CA8" s="255"/>
-      <c r="CB8" s="262" t="s">
+      <c r="BY8" s="407"/>
+      <c r="BZ8" s="407"/>
+      <c r="CA8" s="408"/>
+      <c r="CB8" s="395" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="242" t="s">
+      <c r="CC8" s="395" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="242" t="s">
+      <c r="CD8" s="395" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="300"/>
-      <c r="B9" s="303"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="284" t="s">
+      <c r="A9" s="448"/>
+      <c r="B9" s="451"/>
+      <c r="C9" s="399"/>
+      <c r="D9" s="454"/>
+      <c r="E9" s="454"/>
+      <c r="F9" s="399"/>
+      <c r="G9" s="457"/>
+      <c r="H9" s="427"/>
+      <c r="I9" s="427"/>
+      <c r="J9" s="457"/>
+      <c r="K9" s="434" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="284" t="s">
+      <c r="L9" s="434" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="284" t="s">
+      <c r="M9" s="434" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="284" t="s">
+      <c r="N9" s="434" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="284" t="s">
+      <c r="O9" s="434" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="284" t="s">
+      <c r="P9" s="434" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="284" t="s">
+      <c r="Q9" s="434" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="284" t="s">
+      <c r="R9" s="434" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="284" t="s">
+      <c r="S9" s="434" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="284" t="s">
+      <c r="T9" s="434" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="284" t="s">
+      <c r="U9" s="434" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="293" t="s">
+      <c r="V9" s="443" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="294"/>
-      <c r="X9" s="284" t="s">
+      <c r="W9" s="444"/>
+      <c r="X9" s="434" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="287" t="s">
+      <c r="Y9" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="287" t="s">
+      <c r="Z9" s="437" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="287" t="s">
+      <c r="AA9" s="437" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="287" t="s">
+      <c r="AB9" s="437" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="290" t="s">
+      <c r="AC9" s="440" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="290" t="s">
+      <c r="AD9" s="440" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="290" t="s">
+      <c r="AE9" s="440" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="290" t="s">
+      <c r="AF9" s="440" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="287" t="s">
+      <c r="AG9" s="437" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="290" t="s">
+      <c r="AH9" s="440" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="290" t="s">
+      <c r="AI9" s="440" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="287" t="s">
+      <c r="AJ9" s="437" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="320" t="s">
+      <c r="AK9" s="467" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="245" t="s">
+      <c r="AL9" s="398" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="287" t="s">
+      <c r="AM9" s="437" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="317" t="s">
+      <c r="AN9" s="464" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="245" t="s">
+      <c r="AO9" s="398" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="309"/>
-      <c r="AQ9" s="309"/>
-      <c r="AR9" s="309"/>
-      <c r="AS9" s="309"/>
-      <c r="AT9" s="309"/>
-      <c r="AU9" s="309"/>
-      <c r="AV9" s="246"/>
-      <c r="AW9" s="246"/>
-      <c r="AX9" s="246"/>
-      <c r="AY9" s="313" t="s">
+      <c r="AP9" s="457"/>
+      <c r="AQ9" s="457"/>
+      <c r="AR9" s="457"/>
+      <c r="AS9" s="457"/>
+      <c r="AT9" s="457"/>
+      <c r="AU9" s="457"/>
+      <c r="AV9" s="399"/>
+      <c r="AW9" s="399"/>
+      <c r="AX9" s="399"/>
+      <c r="AY9" s="461" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="314"/>
-      <c r="BA9" s="314"/>
-      <c r="BB9" s="314"/>
-      <c r="BC9" s="314"/>
-      <c r="BD9" s="314"/>
-      <c r="BE9" s="314"/>
-      <c r="BF9" s="314"/>
-      <c r="BG9" s="314"/>
-      <c r="BH9" s="314"/>
-      <c r="BI9" s="314"/>
-      <c r="BJ9" s="314"/>
-      <c r="BK9" s="314"/>
-      <c r="BL9" s="315"/>
-      <c r="BM9" s="313" t="s">
+      <c r="AZ9" s="462"/>
+      <c r="BA9" s="462"/>
+      <c r="BB9" s="462"/>
+      <c r="BC9" s="462"/>
+      <c r="BD9" s="462"/>
+      <c r="BE9" s="462"/>
+      <c r="BF9" s="462"/>
+      <c r="BG9" s="462"/>
+      <c r="BH9" s="462"/>
+      <c r="BI9" s="462"/>
+      <c r="BJ9" s="462"/>
+      <c r="BK9" s="462"/>
+      <c r="BL9" s="463"/>
+      <c r="BM9" s="461" t="s">
         <v>65</v>
       </c>
-      <c r="BN9" s="314"/>
-      <c r="BO9" s="314"/>
-      <c r="BP9" s="314"/>
-      <c r="BQ9" s="315"/>
-      <c r="BR9" s="266" t="s">
+      <c r="BN9" s="462"/>
+      <c r="BO9" s="462"/>
+      <c r="BP9" s="462"/>
+      <c r="BQ9" s="463"/>
+      <c r="BR9" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="266" t="s">
+      <c r="BS9" s="416" t="s">
         <v>67</v>
       </c>
-      <c r="BT9" s="266"/>
-      <c r="BU9" s="269"/>
+      <c r="BT9" s="416"/>
+      <c r="BU9" s="419"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="251"/>
-      <c r="BX9" s="256"/>
-      <c r="BY9" s="257"/>
-      <c r="BZ9" s="257"/>
-      <c r="CA9" s="258"/>
-      <c r="CB9" s="263"/>
-      <c r="CC9" s="243"/>
-      <c r="CD9" s="243"/>
+      <c r="BW9" s="404"/>
+      <c r="BX9" s="409"/>
+      <c r="BY9" s="410"/>
+      <c r="BZ9" s="410"/>
+      <c r="CA9" s="411"/>
+      <c r="CB9" s="396"/>
+      <c r="CC9" s="396"/>
+      <c r="CD9" s="396"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="300"/>
-      <c r="B10" s="303"/>
-      <c r="C10" s="246"/>
-      <c r="D10" s="306"/>
-      <c r="E10" s="306"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="309"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="309"/>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
-      <c r="M10" s="285"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
-      <c r="R10" s="285"/>
-      <c r="S10" s="285"/>
-      <c r="T10" s="285"/>
-      <c r="U10" s="285"/>
-      <c r="V10" s="295"/>
-      <c r="W10" s="296"/>
-      <c r="X10" s="285"/>
-      <c r="Y10" s="288"/>
-      <c r="Z10" s="288"/>
-      <c r="AA10" s="288"/>
-      <c r="AB10" s="288"/>
-      <c r="AC10" s="291"/>
-      <c r="AD10" s="291"/>
-      <c r="AE10" s="291"/>
-      <c r="AF10" s="291"/>
-      <c r="AG10" s="288"/>
-      <c r="AH10" s="291"/>
-      <c r="AI10" s="291"/>
-      <c r="AJ10" s="288"/>
-      <c r="AK10" s="321"/>
-      <c r="AL10" s="246"/>
-      <c r="AM10" s="288"/>
-      <c r="AN10" s="318"/>
-      <c r="AO10" s="246"/>
-      <c r="AP10" s="309"/>
-      <c r="AQ10" s="309"/>
-      <c r="AR10" s="309"/>
-      <c r="AS10" s="309"/>
-      <c r="AT10" s="309"/>
-      <c r="AU10" s="309"/>
-      <c r="AV10" s="246"/>
-      <c r="AW10" s="246"/>
-      <c r="AX10" s="246"/>
+      <c r="A10" s="448"/>
+      <c r="B10" s="451"/>
+      <c r="C10" s="399"/>
+      <c r="D10" s="454"/>
+      <c r="E10" s="454"/>
+      <c r="F10" s="399"/>
+      <c r="G10" s="457"/>
+      <c r="H10" s="427"/>
+      <c r="I10" s="427"/>
+      <c r="J10" s="457"/>
+      <c r="K10" s="435"/>
+      <c r="L10" s="435"/>
+      <c r="M10" s="435"/>
+      <c r="N10" s="435"/>
+      <c r="O10" s="435"/>
+      <c r="P10" s="435"/>
+      <c r="Q10" s="435"/>
+      <c r="R10" s="435"/>
+      <c r="S10" s="435"/>
+      <c r="T10" s="435"/>
+      <c r="U10" s="435"/>
+      <c r="V10" s="445"/>
+      <c r="W10" s="446"/>
+      <c r="X10" s="435"/>
+      <c r="Y10" s="438"/>
+      <c r="Z10" s="438"/>
+      <c r="AA10" s="438"/>
+      <c r="AB10" s="438"/>
+      <c r="AC10" s="441"/>
+      <c r="AD10" s="441"/>
+      <c r="AE10" s="441"/>
+      <c r="AF10" s="441"/>
+      <c r="AG10" s="438"/>
+      <c r="AH10" s="441"/>
+      <c r="AI10" s="441"/>
+      <c r="AJ10" s="438"/>
+      <c r="AK10" s="468"/>
+      <c r="AL10" s="399"/>
+      <c r="AM10" s="438"/>
+      <c r="AN10" s="465"/>
+      <c r="AO10" s="399"/>
+      <c r="AP10" s="457"/>
+      <c r="AQ10" s="457"/>
+      <c r="AR10" s="457"/>
+      <c r="AS10" s="457"/>
+      <c r="AT10" s="457"/>
+      <c r="AU10" s="457"/>
+      <c r="AV10" s="399"/>
+      <c r="AW10" s="399"/>
+      <c r="AX10" s="399"/>
       <c r="AY10" s="101" t="s">
         <v>68</v>
       </c>
@@ -8184,125 +8704,125 @@
       <c r="BA10" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="271" t="s">
+      <c r="BB10" s="421" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="248" t="s">
+      <c r="BC10" s="401" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="248" t="s">
+      <c r="BD10" s="401" t="s">
         <v>73</v>
       </c>
-      <c r="BE10" s="273" t="s">
+      <c r="BE10" s="423" t="s">
         <v>74</v>
       </c>
-      <c r="BF10" s="248" t="s">
+      <c r="BF10" s="401" t="s">
         <v>75</v>
       </c>
-      <c r="BG10" s="248" t="s">
+      <c r="BG10" s="401" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="248" t="s">
+      <c r="BH10" s="401" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="248" t="s">
+      <c r="BI10" s="401" t="s">
         <v>78</v>
       </c>
-      <c r="BJ10" s="248" t="s">
+      <c r="BJ10" s="401" t="s">
         <v>79</v>
       </c>
-      <c r="BK10" s="248" t="s">
+      <c r="BK10" s="401" t="s">
         <v>80</v>
       </c>
-      <c r="BL10" s="311" t="s">
+      <c r="BL10" s="459" t="s">
         <v>81</v>
       </c>
-      <c r="BM10" s="248" t="s">
+      <c r="BM10" s="401" t="s">
         <v>82</v>
       </c>
-      <c r="BN10" s="265" t="s">
+      <c r="BN10" s="415" t="s">
         <v>83</v>
       </c>
-      <c r="BO10" s="248" t="s">
+      <c r="BO10" s="401" t="s">
         <v>84</v>
       </c>
-      <c r="BP10" s="265" t="s">
+      <c r="BP10" s="415" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="265" t="s">
+      <c r="BQ10" s="415" t="s">
         <v>86</v>
       </c>
-      <c r="BR10" s="266"/>
-      <c r="BS10" s="266"/>
-      <c r="BT10" s="266"/>
-      <c r="BU10" s="269"/>
+      <c r="BR10" s="416"/>
+      <c r="BS10" s="416"/>
+      <c r="BT10" s="416"/>
+      <c r="BU10" s="419"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="252"/>
-      <c r="BX10" s="259"/>
-      <c r="BY10" s="260"/>
-      <c r="BZ10" s="260"/>
-      <c r="CA10" s="261"/>
-      <c r="CB10" s="264"/>
-      <c r="CC10" s="244"/>
-      <c r="CD10" s="244"/>
+      <c r="BW10" s="405"/>
+      <c r="BX10" s="412"/>
+      <c r="BY10" s="413"/>
+      <c r="BZ10" s="413"/>
+      <c r="CA10" s="414"/>
+      <c r="CB10" s="397"/>
+      <c r="CC10" s="397"/>
+      <c r="CD10" s="397"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="28">
-      <c r="A11" s="301"/>
-      <c r="B11" s="304"/>
-      <c r="C11" s="247"/>
-      <c r="D11" s="307"/>
-      <c r="E11" s="307"/>
-      <c r="F11" s="247"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="278"/>
-      <c r="I11" s="278"/>
-      <c r="J11" s="310"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286"/>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="286"/>
-      <c r="Q11" s="286"/>
-      <c r="R11" s="286"/>
-      <c r="S11" s="286"/>
-      <c r="T11" s="286"/>
-      <c r="U11" s="286"/>
+      <c r="A11" s="449"/>
+      <c r="B11" s="452"/>
+      <c r="C11" s="400"/>
+      <c r="D11" s="455"/>
+      <c r="E11" s="455"/>
+      <c r="F11" s="400"/>
+      <c r="G11" s="458"/>
+      <c r="H11" s="428"/>
+      <c r="I11" s="428"/>
+      <c r="J11" s="458"/>
+      <c r="K11" s="436"/>
+      <c r="L11" s="436"/>
+      <c r="M11" s="436"/>
+      <c r="N11" s="436"/>
+      <c r="O11" s="436"/>
+      <c r="P11" s="436"/>
+      <c r="Q11" s="436"/>
+      <c r="R11" s="436"/>
+      <c r="S11" s="436"/>
+      <c r="T11" s="436"/>
+      <c r="U11" s="436"/>
       <c r="V11" s="30" t="s">
         <v>87</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="286"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="292"/>
-      <c r="AD11" s="292"/>
-      <c r="AE11" s="292"/>
-      <c r="AF11" s="292"/>
-      <c r="AG11" s="289"/>
-      <c r="AH11" s="292"/>
-      <c r="AI11" s="292"/>
-      <c r="AJ11" s="289"/>
-      <c r="AK11" s="322"/>
-      <c r="AL11" s="247"/>
-      <c r="AM11" s="289"/>
-      <c r="AN11" s="319"/>
-      <c r="AO11" s="247"/>
-      <c r="AP11" s="310"/>
-      <c r="AQ11" s="310"/>
-      <c r="AR11" s="310"/>
-      <c r="AS11" s="310"/>
-      <c r="AT11" s="310"/>
-      <c r="AU11" s="310"/>
-      <c r="AV11" s="247"/>
-      <c r="AW11" s="247"/>
-      <c r="AX11" s="247"/>
+      <c r="X11" s="436"/>
+      <c r="Y11" s="439"/>
+      <c r="Z11" s="439"/>
+      <c r="AA11" s="439"/>
+      <c r="AB11" s="439"/>
+      <c r="AC11" s="442"/>
+      <c r="AD11" s="442"/>
+      <c r="AE11" s="442"/>
+      <c r="AF11" s="442"/>
+      <c r="AG11" s="439"/>
+      <c r="AH11" s="442"/>
+      <c r="AI11" s="442"/>
+      <c r="AJ11" s="439"/>
+      <c r="AK11" s="469"/>
+      <c r="AL11" s="400"/>
+      <c r="AM11" s="439"/>
+      <c r="AN11" s="466"/>
+      <c r="AO11" s="400"/>
+      <c r="AP11" s="458"/>
+      <c r="AQ11" s="458"/>
+      <c r="AR11" s="458"/>
+      <c r="AS11" s="458"/>
+      <c r="AT11" s="458"/>
+      <c r="AU11" s="458"/>
+      <c r="AV11" s="400"/>
+      <c r="AW11" s="400"/>
+      <c r="AX11" s="400"/>
       <c r="AY11" s="102" t="s">
         <v>89</v>
       </c>
@@ -8312,43 +8832,43 @@
       <c r="BA11" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="272"/>
-      <c r="BC11" s="249"/>
-      <c r="BD11" s="249"/>
-      <c r="BE11" s="274"/>
-      <c r="BF11" s="249"/>
-      <c r="BG11" s="249"/>
-      <c r="BH11" s="249"/>
-      <c r="BI11" s="249"/>
-      <c r="BJ11" s="249"/>
-      <c r="BK11" s="249"/>
-      <c r="BL11" s="312"/>
-      <c r="BM11" s="249"/>
-      <c r="BN11" s="267"/>
-      <c r="BO11" s="249"/>
-      <c r="BP11" s="267"/>
-      <c r="BQ11" s="267"/>
-      <c r="BR11" s="267"/>
-      <c r="BS11" s="267"/>
-      <c r="BT11" s="267"/>
-      <c r="BU11" s="270"/>
+      <c r="BB11" s="422"/>
+      <c r="BC11" s="402"/>
+      <c r="BD11" s="402"/>
+      <c r="BE11" s="424"/>
+      <c r="BF11" s="402"/>
+      <c r="BG11" s="402"/>
+      <c r="BH11" s="402"/>
+      <c r="BI11" s="402"/>
+      <c r="BJ11" s="402"/>
+      <c r="BK11" s="402"/>
+      <c r="BL11" s="460"/>
+      <c r="BM11" s="402"/>
+      <c r="BN11" s="417"/>
+      <c r="BO11" s="402"/>
+      <c r="BP11" s="417"/>
+      <c r="BQ11" s="417"/>
+      <c r="BR11" s="417"/>
+      <c r="BS11" s="417"/>
+      <c r="BT11" s="417"/>
+      <c r="BU11" s="420"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="252"/>
-      <c r="BX11" s="72" t="s">
+      <c r="BW11" s="405"/>
+      <c r="BX11" s="338" t="s">
         <v>92</v>
       </c>
-      <c r="BY11" s="72" t="s">
+      <c r="BY11" s="338" t="s">
         <v>93</v>
       </c>
-      <c r="BZ11" s="72" t="s">
+      <c r="BZ11" s="338" t="s">
         <v>94</v>
       </c>
-      <c r="CA11" s="73" t="s">
+      <c r="CA11" s="339" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="264"/>
-      <c r="CC11" s="244"/>
-      <c r="CD11" s="244"/>
+      <c r="CB11" s="397"/>
+      <c r="CC11" s="397"/>
+      <c r="CD11" s="397"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -8871,9 +9391,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="81">
+      <c r="AM14" s="81" t="e">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="AN14" s="81">
         <f t="shared" ref="AN14:BT14" si="10">SUM(AN15:AN21)</f>
@@ -8889,9 +9409,9 @@
       <c r="AS14" s="81"/>
       <c r="AT14" s="81"/>
       <c r="AU14" s="81"/>
-      <c r="AV14" s="81">
+      <c r="AV14" s="81" t="e">
         <f t="shared" si="10"/>
-        <v>239266923.07692307</v>
+        <v>#REF!</v>
       </c>
       <c r="AW14" s="81"/>
       <c r="AX14" s="81"/>
@@ -8926,9 +9446,9 @@
       <c r="BI14" s="81"/>
       <c r="BJ14" s="81"/>
       <c r="BK14" s="81"/>
-      <c r="BL14" s="81">
+      <c r="BL14" s="81" t="e">
         <f t="shared" si="10"/>
-        <v>20461490</v>
+        <v>#REF!</v>
       </c>
       <c r="BM14" s="81">
         <f t="shared" si="10"/>
@@ -8956,9 +9476,9 @@
         <f t="shared" si="10"/>
         <v>92038615.384615406</v>
       </c>
-      <c r="BU14" s="104">
+      <c r="BU14" s="104" t="e">
         <f t="shared" ref="BU14" si="11">SUM(BU15:BU21)</f>
-        <v>121611917.6923077</v>
+        <v>#REF!</v>
       </c>
       <c r="BV14" s="117"/>
       <c r="BW14" s="108"/>
@@ -8994,7 +9514,7 @@
         <v>9520000</v>
       </c>
       <c r="H15" s="91">
-        <f t="shared" ref="H15:H21" si="12">+IF(OR(CC15="ĐT PCCC",CC15="ĐP PCCC"),780000,IF(CC15="AT-VSV",300000,0))</f>
+        <f>+IF(OR(CD15="ĐT PCCC",CD15="ĐP PCCC"),780000,IF(CD15="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
       <c r="I15" s="91">
@@ -9045,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="91">
-        <f t="shared" ref="Y15:Y21" si="13">G15*(K15+L15)/26</f>
+        <f t="shared" ref="Y15:Y21" si="12">G15*(K15+L15)/26</f>
         <v>9520000</v>
       </c>
       <c r="Z15" s="91">
@@ -9081,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="91">
-        <f t="shared" ref="AH15:AH21" si="14">CB15/26*U15</f>
+        <f t="shared" ref="AH15:AH21" si="13">CB15/26*U15</f>
         <v>0</v>
       </c>
       <c r="AI15" s="91">
@@ -9090,20 +9610,20 @@
       </c>
       <c r="AJ15" s="91"/>
       <c r="AK15" s="91">
-        <f t="shared" ref="AK15:AK21" si="15">BZ15*L15/26</f>
+        <f t="shared" ref="AK15:AK21" si="14">BZ15*L15/26</f>
         <v>0</v>
       </c>
       <c r="AL15" s="91"/>
-      <c r="AM15" s="91">
-        <f t="shared" ref="AM15:AM21" si="16">X15*CD15</f>
-        <v>0</v>
+      <c r="AM15" s="91" t="e">
+        <f>X15*#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="AN15" s="91">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
       <c r="AO15" s="91">
-        <f t="shared" ref="AO15:AO21" si="17">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15,I15-I15*($CF$3-K15-L15)/26+(H15+I15)*50%*M15/26+BW15*O15/26-AB15+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15+(G15-G15*($CF$3-K15-L15)/26-Y15)+(H15-H15*($CF$3-K15-L15)/26-AN15))</f>
+        <f t="shared" ref="AO15:AO21" si="15">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15,I15-I15*($CF$3-K15-L15)/26+(H15+I15)*50%*M15/26+BW15*O15/26-AB15+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15+(G15-G15*($CF$3-K15-L15)/26-Y15)+(H15-H15*($CF$3-K15-L15)/26-AN15))</f>
         <v>50480000</v>
       </c>
       <c r="AP15" s="91"/>
@@ -9114,9 +9634,9 @@
       <c r="AS15" s="91"/>
       <c r="AT15" s="91"/>
       <c r="AU15" s="91"/>
-      <c r="AV15" s="94">
+      <c r="AV15" s="94" t="e">
         <f>Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
-        <v>61000000</v>
+        <v>#REF!</v>
       </c>
       <c r="AW15" s="94"/>
       <c r="AX15" s="94" t="s">
@@ -9131,7 +9651,7 @@
         <v>142800</v>
       </c>
       <c r="BA15" s="85">
-        <f t="shared" ref="BA15" si="18">ROUND(IF($AX15="x",($G15+$H15)*BA$11,0),0)</f>
+        <f t="shared" ref="BA15" si="16">ROUND(IF($AX15="x",($G15+$H15)*BA$11,0),0)</f>
         <v>95200</v>
       </c>
       <c r="BB15" s="85">
@@ -9144,13 +9664,13 @@
         <f>IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="85">
+      <c r="BF15" s="85" t="e">
         <f>AM15+IF(E15="CT",IF(AR15&gt;=730000,730000,AR15),0)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;"0",((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
-        <v>730000</v>
-      </c>
-      <c r="BG15" s="85">
+        <v>#REF!</v>
+      </c>
+      <c r="BG15" s="85" t="e">
         <f>AV15-BF15+AW15</f>
-        <v>60270000</v>
+        <v>#REF!</v>
       </c>
       <c r="BH15" s="85">
         <v>3</v>
@@ -9159,16 +9679,16 @@
         <v>4400000</v>
       </c>
       <c r="BJ15" s="85">
-        <f t="shared" ref="BJ15:BJ21" si="19">IF(E15="CT",11000000,0)</f>
+        <f t="shared" ref="BJ15:BJ21" si="17">IF(E15="CT",11000000,0)</f>
         <v>11000000</v>
       </c>
-      <c r="BK15" s="85">
+      <c r="BK15" s="85" t="e">
         <f>BG15-BB15-BC15+BD15-BH15*BI15-BJ15</f>
-        <v>35070400</v>
-      </c>
-      <c r="BL15" s="84">
+        <v>#REF!</v>
+      </c>
+      <c r="BL15" s="84" t="e">
         <f>IF(E15="TV",BK15*10%,IF(BK15&gt;0,ROUND(IF(BK15&gt;=80000000,BK15*35%-9850000,IF(BK15&gt;=52000000,BK15*30%-5850000,IF(BK15&gt;=32000000,BK15*25%-3250000,IF(BK15&gt;=18000000,BK15*20%-1650000,IF(BK15&gt;=10000000,BK15*15%-750000,IF(BK15&gt;5000000,BK15*10%-250000,BK15*5%)))))),0),0))</f>
-        <v>5517600</v>
+        <v>#REF!</v>
       </c>
       <c r="BM15" s="85"/>
       <c r="BN15" s="85"/>
@@ -9183,9 +9703,9 @@
         <f>SUMIFS('Bảng lương tạm ứng kỳ 1'!BT:BT,'Bảng lương CB-NV'!B:B,'Bảng lương tạm ứng kỳ 1'!B15)</f>
         <v>25846153.846153852</v>
       </c>
-      <c r="BU15" s="105">
+      <c r="BU15" s="105" t="e">
         <f>AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
-        <v>28541446.153846148</v>
+        <v>#REF!</v>
       </c>
       <c r="BV15" s="118"/>
       <c r="BW15" s="108">
@@ -9205,7 +9725,6 @@
         <f>SUM(BW15:CA15)</f>
         <v>60200000</v>
       </c>
-      <c r="CC15" s="84"/>
       <c r="CD15" s="84"/>
       <c r="CE15" s="95"/>
       <c r="CF15" s="96"/>
@@ -9237,11 +9756,11 @@
         <v>8480000</v>
       </c>
       <c r="H16" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H16:H21" si="18">+IF(OR(CC16="ĐT PCCC",CC16="ĐP PCCC"),780000,IF(CC16="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
       <c r="I16" s="91">
-        <f t="shared" ref="I16:I21" si="20">CB16-BZ16-G16-H16</f>
+        <f t="shared" ref="I16:I21" si="19">CB16-BZ16-G16-H16</f>
         <v>43520000</v>
       </c>
       <c r="J16" s="92">
@@ -9288,31 +9807,31 @@
         <v>0</v>
       </c>
       <c r="Y16" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>7827692.307692308</v>
       </c>
       <c r="Z16" s="91">
-        <f t="shared" ref="Z16:Z17" si="21">M16*G16/26</f>
+        <f t="shared" ref="Z16:Z17" si="20">M16*G16/26</f>
         <v>0</v>
       </c>
       <c r="AA16" s="91">
-        <f t="shared" ref="AA16:AA17" si="22">G16*N16/26</f>
+        <f t="shared" ref="AA16:AA17" si="21">G16*N16/26</f>
         <v>0</v>
       </c>
       <c r="AB16" s="91">
-        <f t="shared" ref="AB16:AB17" si="23">G16*O16/26</f>
+        <f t="shared" ref="AB16:AB17" si="22">G16*O16/26</f>
         <v>0</v>
       </c>
       <c r="AC16" s="91">
-        <f t="shared" ref="AC16:AC17" si="24">G16*P16*150%/26</f>
+        <f t="shared" ref="AC16:AC17" si="23">G16*P16*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD16" s="91">
-        <f t="shared" ref="AD16:AD17" si="25">G16*Q16/26*200%</f>
+        <f t="shared" ref="AD16:AD17" si="24">G16*Q16/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE16" s="91">
-        <f t="shared" ref="AE16:AE17" si="26">G16*R16/26*300%</f>
+        <f t="shared" ref="AE16:AE17" si="25">G16*R16/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF16" s="91">
@@ -9320,25 +9839,25 @@
         <v>0</v>
       </c>
       <c r="AG16" s="91">
-        <f t="shared" ref="AG16:AG17" si="27">T16*G16/26/8</f>
+        <f t="shared" ref="AG16:AG17" si="26">T16*G16/26/8</f>
         <v>0</v>
       </c>
       <c r="AH16" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AI16" s="91">
-        <f t="shared" ref="AI16:AI17" si="28">G16*V16/26</f>
+        <f t="shared" ref="AI16:AI17" si="27">G16*V16/26</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="91"/>
       <c r="AK16" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>38461.538461538461</v>
       </c>
       <c r="AL16" s="91"/>
       <c r="AM16" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="AM16:AM21" si="28">X16*CD16</f>
         <v>0</v>
       </c>
       <c r="AN16" s="91">
@@ -9346,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>40172307.692307696</v>
       </c>
       <c r="AP16" s="91"/>
@@ -9401,7 +9920,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ16" s="85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>11000000</v>
       </c>
       <c r="BK16" s="85">
@@ -9482,11 +10001,11 @@
         <v>7820000</v>
       </c>
       <c r="H17" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I17" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>34180000</v>
       </c>
       <c r="J17" s="92">
@@ -9533,31 +10052,31 @@
         <v>0</v>
       </c>
       <c r="Y17" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>7218461.538461538</v>
       </c>
       <c r="Z17" s="91">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="91">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="91">
+      <c r="AB17" s="91">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="91">
+      <c r="AC17" s="91">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="91">
+      <c r="AD17" s="91">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AD17" s="91">
+      <c r="AE17" s="91">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="91">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF17" s="91">
@@ -9565,25 +10084,25 @@
         <v>0</v>
       </c>
       <c r="AG17" s="91">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="91">
+        <f t="shared" si="13"/>
+        <v>3246153.846153846</v>
+      </c>
+      <c r="AI17" s="91">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="91">
-        <f t="shared" si="14"/>
-        <v>3246153.846153846</v>
-      </c>
-      <c r="AI17" s="91">
-        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="91"/>
       <c r="AK17" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AL17" s="91"/>
       <c r="AM17" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AN17" s="91">
@@ -9591,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="AO17" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>34796923.07692308</v>
       </c>
       <c r="AP17" s="91"/>
@@ -9646,7 +10165,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ17" s="85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>11000000</v>
       </c>
       <c r="BK17" s="85">
@@ -9727,11 +10246,11 @@
         <v>6990000</v>
       </c>
       <c r="H18" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I18" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>19160000</v>
       </c>
       <c r="J18" s="92">
@@ -9778,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="Y18" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6990000</v>
       </c>
       <c r="Z18" s="91">
@@ -9814,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="AH18" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AI18" s="91">
@@ -9823,12 +10342,12 @@
       </c>
       <c r="AJ18" s="91"/>
       <c r="AK18" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>23076.923076923078</v>
       </c>
       <c r="AL18" s="91"/>
       <c r="AM18" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AN18" s="91">
@@ -9836,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>19160000</v>
       </c>
       <c r="AP18" s="91"/>
@@ -9891,7 +10410,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ18" s="85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>11000000</v>
       </c>
       <c r="BK18" s="85">
@@ -9972,11 +10491,11 @@
         <v>4850000</v>
       </c>
       <c r="H19" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I19" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>6700000</v>
       </c>
       <c r="J19" s="92">
@@ -10023,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="Y19" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4103846.153846154</v>
       </c>
       <c r="Z19" s="91">
@@ -10059,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AI19" s="91">
@@ -10068,12 +10587,12 @@
       </c>
       <c r="AJ19" s="91"/>
       <c r="AK19" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AL19" s="91"/>
       <c r="AM19" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AN19" s="91">
@@ -10081,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>6661153.846153846</v>
       </c>
       <c r="AP19" s="91"/>
@@ -10136,7 +10655,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ19" s="85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>11000000</v>
       </c>
       <c r="BK19" s="85">
@@ -10217,11 +10736,11 @@
         <v>6340000</v>
       </c>
       <c r="H20" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>780000</v>
       </c>
       <c r="I20" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>17030000</v>
       </c>
       <c r="J20" s="92">
@@ -10268,7 +10787,7 @@
         <v>0</v>
       </c>
       <c r="Y20" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6340000</v>
       </c>
       <c r="Z20" s="91">
@@ -10304,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="AH20" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AI20" s="91">
@@ -10313,12 +10832,12 @@
       </c>
       <c r="AJ20" s="91"/>
       <c r="AK20" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AL20" s="91"/>
       <c r="AM20" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AN20" s="91">
@@ -10326,7 +10845,7 @@
         <v>780000</v>
       </c>
       <c r="AO20" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>17030000</v>
       </c>
       <c r="AP20" s="91"/>
@@ -10381,7 +10900,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ20" s="85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BK20" s="85">
@@ -10464,11 +10983,11 @@
         <v>6340000</v>
       </c>
       <c r="H21" s="91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>300000</v>
       </c>
       <c r="I21" s="91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>11210000</v>
       </c>
       <c r="J21" s="92">
@@ -10515,7 +11034,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6340000</v>
       </c>
       <c r="Z21" s="91">
@@ -10551,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AI21" s="91">
@@ -10560,12 +11079,12 @@
       </c>
       <c r="AJ21" s="91"/>
       <c r="AK21" s="91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AL21" s="91"/>
       <c r="AM21" s="91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AN21" s="91">
@@ -10573,7 +11092,7 @@
         <v>300000</v>
       </c>
       <c r="AO21" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>12982692.307692306</v>
       </c>
       <c r="AP21" s="91"/>
@@ -10628,7 +11147,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ21" s="85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>11000000</v>
       </c>
       <c r="BK21" s="85">
@@ -10875,89 +11394,9 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
-  <mergeCells count="82">
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="AW8:AW11"/>
+  <mergeCells count="2">
+    <mergeCell ref="BW3:CB6"/>
     <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="BR9:BR11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 C12:BU12 B15:B1048576">
     <cfRule type="duplicateValues" dxfId="23" priority="36"/>
@@ -11170,91 +11609,91 @@
       <c r="CD2" s="137"/>
     </row>
     <row r="3" spans="1:87" s="139" customFormat="1" outlineLevel="1">
-      <c r="A3" s="333" t="str">
+      <c r="A3" s="295" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
-        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2025</v>
-      </c>
-      <c r="B3" s="333"/>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333"/>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
-      <c r="I3" s="333"/>
-      <c r="J3" s="333"/>
-      <c r="K3" s="333"/>
-      <c r="L3" s="333"/>
-      <c r="M3" s="333"/>
-      <c r="N3" s="333"/>
-      <c r="O3" s="333"/>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
-      <c r="Y3" s="333"/>
-      <c r="Z3" s="333"/>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333"/>
-      <c r="AE3" s="333"/>
-      <c r="AF3" s="333"/>
-      <c r="AG3" s="333"/>
-      <c r="AH3" s="333"/>
-      <c r="AI3" s="333"/>
-      <c r="AJ3" s="333"/>
-      <c r="AK3" s="333"/>
-      <c r="AL3" s="333"/>
-      <c r="AM3" s="333"/>
-      <c r="AN3" s="333"/>
-      <c r="AO3" s="333"/>
-      <c r="AP3" s="333"/>
-      <c r="AQ3" s="333"/>
-      <c r="AR3" s="333"/>
-      <c r="AS3" s="333"/>
-      <c r="AT3" s="333"/>
-      <c r="AU3" s="333"/>
-      <c r="AV3" s="333"/>
-      <c r="AW3" s="333"/>
-      <c r="AX3" s="333"/>
-      <c r="AY3" s="333"/>
-      <c r="AZ3" s="333"/>
-      <c r="BA3" s="333"/>
-      <c r="BB3" s="333"/>
-      <c r="BC3" s="333"/>
-      <c r="BD3" s="333"/>
-      <c r="BE3" s="333"/>
-      <c r="BF3" s="333"/>
-      <c r="BG3" s="333"/>
-      <c r="BH3" s="333"/>
-      <c r="BI3" s="333"/>
-      <c r="BJ3" s="333"/>
-      <c r="BK3" s="333"/>
-      <c r="BL3" s="333"/>
-      <c r="BM3" s="333"/>
-      <c r="BN3" s="333"/>
-      <c r="BO3" s="333"/>
-      <c r="BP3" s="333"/>
-      <c r="BQ3" s="333"/>
-      <c r="BR3" s="333"/>
-      <c r="BS3" s="333"/>
-      <c r="BT3" s="333"/>
-      <c r="BU3" s="333"/>
+        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
+      </c>
+      <c r="B3" s="295"/>
+      <c r="C3" s="295"/>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="295"/>
+      <c r="K3" s="295"/>
+      <c r="L3" s="295"/>
+      <c r="M3" s="295"/>
+      <c r="N3" s="295"/>
+      <c r="O3" s="295"/>
+      <c r="P3" s="295"/>
+      <c r="Q3" s="295"/>
+      <c r="R3" s="295"/>
+      <c r="S3" s="295"/>
+      <c r="T3" s="295"/>
+      <c r="U3" s="295"/>
+      <c r="V3" s="295"/>
+      <c r="W3" s="295"/>
+      <c r="X3" s="295"/>
+      <c r="Y3" s="295"/>
+      <c r="Z3" s="295"/>
+      <c r="AA3" s="295"/>
+      <c r="AB3" s="295"/>
+      <c r="AC3" s="295"/>
+      <c r="AD3" s="295"/>
+      <c r="AE3" s="295"/>
+      <c r="AF3" s="295"/>
+      <c r="AG3" s="295"/>
+      <c r="AH3" s="295"/>
+      <c r="AI3" s="295"/>
+      <c r="AJ3" s="295"/>
+      <c r="AK3" s="295"/>
+      <c r="AL3" s="295"/>
+      <c r="AM3" s="295"/>
+      <c r="AN3" s="295"/>
+      <c r="AO3" s="295"/>
+      <c r="AP3" s="295"/>
+      <c r="AQ3" s="295"/>
+      <c r="AR3" s="295"/>
+      <c r="AS3" s="295"/>
+      <c r="AT3" s="295"/>
+      <c r="AU3" s="295"/>
+      <c r="AV3" s="295"/>
+      <c r="AW3" s="295"/>
+      <c r="AX3" s="295"/>
+      <c r="AY3" s="295"/>
+      <c r="AZ3" s="295"/>
+      <c r="BA3" s="295"/>
+      <c r="BB3" s="295"/>
+      <c r="BC3" s="295"/>
+      <c r="BD3" s="295"/>
+      <c r="BE3" s="295"/>
+      <c r="BF3" s="295"/>
+      <c r="BG3" s="295"/>
+      <c r="BH3" s="295"/>
+      <c r="BI3" s="295"/>
+      <c r="BJ3" s="295"/>
+      <c r="BK3" s="295"/>
+      <c r="BL3" s="295"/>
+      <c r="BM3" s="295"/>
+      <c r="BN3" s="295"/>
+      <c r="BO3" s="295"/>
+      <c r="BP3" s="295"/>
+      <c r="BQ3" s="295"/>
+      <c r="BR3" s="295"/>
+      <c r="BS3" s="295"/>
+      <c r="BT3" s="295"/>
+      <c r="BU3" s="295"/>
       <c r="BV3"/>
-      <c r="BW3" s="334" t="s">
+      <c r="BW3" s="296" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="334"/>
-      <c r="BY3" s="334"/>
-      <c r="BZ3" s="334"/>
-      <c r="CA3" s="334"/>
-      <c r="CB3" s="333"/>
+      <c r="BX3" s="296"/>
+      <c r="BY3" s="296"/>
+      <c r="BZ3" s="296"/>
+      <c r="CA3" s="296"/>
+      <c r="CB3" s="295"/>
       <c r="CC3" s="138"/>
       <c r="CD3" s="138"/>
       <c r="CE3" s="139" t="s">
@@ -11338,29 +11777,29 @@
       <c r="BT4" s="140"/>
       <c r="BU4" s="140"/>
       <c r="BV4"/>
-      <c r="BW4" s="333"/>
-      <c r="BX4" s="333"/>
-      <c r="BY4" s="333"/>
-      <c r="BZ4" s="333"/>
-      <c r="CA4" s="333"/>
-      <c r="CB4" s="333"/>
+      <c r="BW4" s="295"/>
+      <c r="BX4" s="295"/>
+      <c r="BY4" s="295"/>
+      <c r="BZ4" s="295"/>
+      <c r="CA4" s="295"/>
+      <c r="CB4" s="295"/>
       <c r="CC4" s="138"/>
       <c r="CD4" s="138"/>
     </row>
     <row r="5" spans="1:87" s="141" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="299" t="s">
+      <c r="A5" s="263" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="302" t="s">
+      <c r="B5" s="266" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="305" t="s">
+      <c r="D5" s="258" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="305" t="s">
+      <c r="E5" s="258" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="245" t="s">
@@ -11369,50 +11808,50 @@
       <c r="G5" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="323" t="s">
+      <c r="H5" s="297" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="323" t="s">
+      <c r="I5" s="297" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="245" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="335" t="s">
+      <c r="K5" s="300" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="336"/>
-      <c r="M5" s="336"/>
-      <c r="N5" s="336"/>
-      <c r="O5" s="336"/>
-      <c r="P5" s="336"/>
-      <c r="Q5" s="336"/>
-      <c r="R5" s="336"/>
-      <c r="S5" s="336"/>
-      <c r="T5" s="336"/>
-      <c r="U5" s="336"/>
-      <c r="V5" s="336"/>
-      <c r="W5" s="336"/>
-      <c r="X5" s="357"/>
-      <c r="Y5" s="337" t="s">
+      <c r="L5" s="301"/>
+      <c r="M5" s="301"/>
+      <c r="N5" s="301"/>
+      <c r="O5" s="301"/>
+      <c r="P5" s="301"/>
+      <c r="Q5" s="301"/>
+      <c r="R5" s="301"/>
+      <c r="S5" s="301"/>
+      <c r="T5" s="301"/>
+      <c r="U5" s="301"/>
+      <c r="V5" s="301"/>
+      <c r="W5" s="301"/>
+      <c r="X5" s="302"/>
+      <c r="Y5" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="338"/>
-      <c r="AA5" s="338"/>
-      <c r="AB5" s="338"/>
-      <c r="AC5" s="338"/>
-      <c r="AD5" s="338"/>
-      <c r="AE5" s="338"/>
-      <c r="AF5" s="338"/>
-      <c r="AG5" s="338"/>
-      <c r="AH5" s="338"/>
-      <c r="AI5" s="338"/>
-      <c r="AJ5" s="338"/>
-      <c r="AK5" s="338"/>
-      <c r="AL5" s="338"/>
-      <c r="AM5" s="338"/>
-      <c r="AN5" s="338"/>
-      <c r="AO5" s="339"/>
+      <c r="Z5" s="304"/>
+      <c r="AA5" s="304"/>
+      <c r="AB5" s="304"/>
+      <c r="AC5" s="304"/>
+      <c r="AD5" s="304"/>
+      <c r="AE5" s="304"/>
+      <c r="AF5" s="304"/>
+      <c r="AG5" s="304"/>
+      <c r="AH5" s="304"/>
+      <c r="AI5" s="304"/>
+      <c r="AJ5" s="304"/>
+      <c r="AK5" s="304"/>
+      <c r="AL5" s="304"/>
+      <c r="AM5" s="304"/>
+      <c r="AN5" s="304"/>
+      <c r="AO5" s="305"/>
       <c r="AP5" s="245" t="s">
         <v>16</v>
       </c>
@@ -11440,108 +11879,108 @@
       <c r="AX5" s="245" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="313" t="s">
+      <c r="AY5" s="248" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="314"/>
-      <c r="BA5" s="314"/>
-      <c r="BB5" s="314"/>
-      <c r="BC5" s="314"/>
-      <c r="BD5" s="314"/>
-      <c r="BE5" s="314"/>
-      <c r="BF5" s="314"/>
-      <c r="BG5" s="314"/>
-      <c r="BH5" s="314"/>
-      <c r="BI5" s="314"/>
-      <c r="BJ5" s="314"/>
-      <c r="BK5" s="314"/>
-      <c r="BL5" s="314"/>
-      <c r="BM5" s="314"/>
-      <c r="BN5" s="314"/>
-      <c r="BO5" s="314"/>
-      <c r="BP5" s="314"/>
-      <c r="BQ5" s="315"/>
-      <c r="BR5" s="268" t="s">
+      <c r="AZ5" s="249"/>
+      <c r="BA5" s="249"/>
+      <c r="BB5" s="249"/>
+      <c r="BC5" s="249"/>
+      <c r="BD5" s="249"/>
+      <c r="BE5" s="249"/>
+      <c r="BF5" s="249"/>
+      <c r="BG5" s="249"/>
+      <c r="BH5" s="249"/>
+      <c r="BI5" s="249"/>
+      <c r="BJ5" s="249"/>
+      <c r="BK5" s="249"/>
+      <c r="BL5" s="249"/>
+      <c r="BM5" s="249"/>
+      <c r="BN5" s="249"/>
+      <c r="BO5" s="249"/>
+      <c r="BP5" s="249"/>
+      <c r="BQ5" s="250"/>
+      <c r="BR5" s="289" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="275"/>
-      <c r="BT5" s="265" t="s">
+      <c r="BS5" s="294"/>
+      <c r="BT5" s="257" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="268" t="s">
+      <c r="BU5" s="289" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="351" t="s">
+      <c r="BW5" s="317" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="253" t="s">
+      <c r="BX5" s="277" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="254"/>
-      <c r="BZ5" s="254"/>
-      <c r="CA5" s="255"/>
-      <c r="CB5" s="355" t="s">
+      <c r="BY5" s="278"/>
+      <c r="BZ5" s="278"/>
+      <c r="CA5" s="279"/>
+      <c r="CB5" s="313" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="353" t="s">
+      <c r="CC5" s="315" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="353" t="s">
+      <c r="CD5" s="315" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="142"/>
       <c r="CI5" s="143"/>
     </row>
     <row r="6" spans="1:87" s="141" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="300"/>
-      <c r="B6" s="303"/>
+      <c r="A6" s="264"/>
+      <c r="B6" s="267"/>
       <c r="C6" s="246"/>
-      <c r="D6" s="306"/>
-      <c r="E6" s="306"/>
+      <c r="D6" s="259"/>
+      <c r="E6" s="259"/>
       <c r="F6" s="246"/>
       <c r="G6" s="246"/>
-      <c r="H6" s="324"/>
-      <c r="I6" s="324"/>
+      <c r="H6" s="298"/>
+      <c r="I6" s="298"/>
       <c r="J6" s="246"/>
-      <c r="K6" s="326" t="s">
+      <c r="K6" s="306" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="326" t="s">
+      <c r="L6" s="306" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="326" t="s">
+      <c r="M6" s="306" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="326" t="s">
+      <c r="N6" s="306" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="326" t="s">
+      <c r="O6" s="306" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="326" t="s">
+      <c r="P6" s="306" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="326" t="s">
+      <c r="Q6" s="306" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="326" t="s">
+      <c r="R6" s="306" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="326" t="s">
+      <c r="S6" s="306" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="326" t="s">
+      <c r="T6" s="306" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="326" t="s">
+      <c r="U6" s="306" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="329" t="s">
+      <c r="V6" s="309" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="330"/>
-      <c r="X6" s="326" t="s">
+      <c r="W6" s="310"/>
+      <c r="X6" s="306" t="s">
         <v>46</v>
       </c>
       <c r="Y6" s="245" t="s">
@@ -11556,25 +11995,25 @@
       <c r="AB6" s="245" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="323" t="s">
+      <c r="AC6" s="297" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="323" t="s">
+      <c r="AD6" s="297" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="323" t="s">
+      <c r="AE6" s="297" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="323" t="s">
+      <c r="AF6" s="297" t="s">
         <v>54</v>
       </c>
       <c r="AG6" s="245" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="323" t="s">
+      <c r="AH6" s="297" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="323" t="s">
+      <c r="AI6" s="297" t="s">
         <v>57</v>
       </c>
       <c r="AJ6" s="245" t="s">
@@ -11589,7 +12028,7 @@
       <c r="AM6" s="245" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="317" t="s">
+      <c r="AN6" s="252" t="s">
         <v>62</v>
       </c>
       <c r="AO6" s="245" t="s">
@@ -11604,90 +12043,90 @@
       <c r="AV6" s="246"/>
       <c r="AW6" s="246"/>
       <c r="AX6" s="246"/>
-      <c r="AY6" s="313" t="s">
+      <c r="AY6" s="248" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="314"/>
-      <c r="BA6" s="314"/>
-      <c r="BB6" s="314"/>
-      <c r="BC6" s="314"/>
-      <c r="BD6" s="314"/>
-      <c r="BE6" s="314"/>
-      <c r="BF6" s="314"/>
-      <c r="BG6" s="314"/>
-      <c r="BH6" s="314"/>
-      <c r="BI6" s="314"/>
-      <c r="BJ6" s="314"/>
-      <c r="BK6" s="314"/>
-      <c r="BL6" s="315"/>
-      <c r="BM6" s="313" t="s">
+      <c r="AZ6" s="249"/>
+      <c r="BA6" s="249"/>
+      <c r="BB6" s="249"/>
+      <c r="BC6" s="249"/>
+      <c r="BD6" s="249"/>
+      <c r="BE6" s="249"/>
+      <c r="BF6" s="249"/>
+      <c r="BG6" s="249"/>
+      <c r="BH6" s="249"/>
+      <c r="BI6" s="249"/>
+      <c r="BJ6" s="249"/>
+      <c r="BK6" s="249"/>
+      <c r="BL6" s="250"/>
+      <c r="BM6" s="248" t="s">
         <v>65</v>
       </c>
-      <c r="BN6" s="314"/>
-      <c r="BO6" s="314"/>
-      <c r="BP6" s="314"/>
-      <c r="BQ6" s="315"/>
-      <c r="BR6" s="266" t="s">
+      <c r="BN6" s="249"/>
+      <c r="BO6" s="249"/>
+      <c r="BP6" s="249"/>
+      <c r="BQ6" s="250"/>
+      <c r="BR6" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="266" t="s">
+      <c r="BS6" s="255" t="s">
         <v>67</v>
       </c>
-      <c r="BT6" s="266"/>
-      <c r="BU6" s="269"/>
+      <c r="BT6" s="255"/>
+      <c r="BU6" s="290"/>
       <c r="BV6"/>
-      <c r="BW6" s="352"/>
-      <c r="BX6" s="256"/>
-      <c r="BY6" s="257"/>
-      <c r="BZ6" s="257"/>
-      <c r="CA6" s="258"/>
-      <c r="CB6" s="356"/>
-      <c r="CC6" s="354"/>
-      <c r="CD6" s="354"/>
+      <c r="BW6" s="318"/>
+      <c r="BX6" s="280"/>
+      <c r="BY6" s="281"/>
+      <c r="BZ6" s="281"/>
+      <c r="CA6" s="282"/>
+      <c r="CB6" s="314"/>
+      <c r="CC6" s="316"/>
+      <c r="CD6" s="316"/>
       <c r="CH6" s="142"/>
       <c r="CI6" s="143"/>
     </row>
     <row r="7" spans="1:87" s="144" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="300"/>
-      <c r="B7" s="303"/>
+      <c r="A7" s="264"/>
+      <c r="B7" s="267"/>
       <c r="C7" s="246"/>
-      <c r="D7" s="306"/>
-      <c r="E7" s="306"/>
+      <c r="D7" s="259"/>
+      <c r="E7" s="259"/>
       <c r="F7" s="246"/>
       <c r="G7" s="246"/>
-      <c r="H7" s="324"/>
-      <c r="I7" s="324"/>
+      <c r="H7" s="298"/>
+      <c r="I7" s="298"/>
       <c r="J7" s="246"/>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
-      <c r="O7" s="327"/>
-      <c r="P7" s="327"/>
-      <c r="Q7" s="327"/>
-      <c r="R7" s="327"/>
-      <c r="S7" s="327"/>
-      <c r="T7" s="327"/>
-      <c r="U7" s="327"/>
-      <c r="V7" s="331"/>
-      <c r="W7" s="332"/>
-      <c r="X7" s="327"/>
+      <c r="K7" s="307"/>
+      <c r="L7" s="307"/>
+      <c r="M7" s="307"/>
+      <c r="N7" s="307"/>
+      <c r="O7" s="307"/>
+      <c r="P7" s="307"/>
+      <c r="Q7" s="307"/>
+      <c r="R7" s="307"/>
+      <c r="S7" s="307"/>
+      <c r="T7" s="307"/>
+      <c r="U7" s="307"/>
+      <c r="V7" s="311"/>
+      <c r="W7" s="312"/>
+      <c r="X7" s="307"/>
       <c r="Y7" s="246"/>
       <c r="Z7" s="246"/>
       <c r="AA7" s="246"/>
       <c r="AB7" s="246"/>
-      <c r="AC7" s="324"/>
-      <c r="AD7" s="324"/>
-      <c r="AE7" s="324"/>
-      <c r="AF7" s="324"/>
+      <c r="AC7" s="298"/>
+      <c r="AD7" s="298"/>
+      <c r="AE7" s="298"/>
+      <c r="AF7" s="298"/>
       <c r="AG7" s="246"/>
-      <c r="AH7" s="324"/>
-      <c r="AI7" s="324"/>
+      <c r="AH7" s="298"/>
+      <c r="AI7" s="298"/>
       <c r="AJ7" s="246"/>
       <c r="AK7" s="246"/>
       <c r="AL7" s="246"/>
       <c r="AM7" s="246"/>
-      <c r="AN7" s="318"/>
+      <c r="AN7" s="253"/>
       <c r="AO7" s="246"/>
       <c r="AP7" s="246"/>
       <c r="AQ7" s="246"/>
@@ -11707,115 +12146,115 @@
       <c r="BA7" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="265" t="s">
+      <c r="BB7" s="257" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="248" t="s">
+      <c r="BC7" s="240" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="248" t="s">
+      <c r="BD7" s="240" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="273" t="s">
+      <c r="BE7" s="292" t="s">
         <v>74</v>
       </c>
-      <c r="BF7" s="248" t="s">
+      <c r="BF7" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="248" t="s">
+      <c r="BG7" s="240" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="248" t="s">
+      <c r="BH7" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="248" t="s">
+      <c r="BI7" s="240" t="s">
         <v>78</v>
       </c>
-      <c r="BJ7" s="248" t="s">
+      <c r="BJ7" s="240" t="s">
         <v>79</v>
       </c>
-      <c r="BK7" s="248" t="s">
+      <c r="BK7" s="240" t="s">
         <v>80</v>
       </c>
-      <c r="BL7" s="311" t="s">
+      <c r="BL7" s="269" t="s">
         <v>81</v>
       </c>
-      <c r="BM7" s="248" t="s">
+      <c r="BM7" s="240" t="s">
         <v>82</v>
       </c>
-      <c r="BN7" s="265" t="s">
+      <c r="BN7" s="257" t="s">
         <v>83</v>
       </c>
-      <c r="BO7" s="248" t="s">
+      <c r="BO7" s="240" t="s">
         <v>84</v>
       </c>
-      <c r="BP7" s="265" t="s">
+      <c r="BP7" s="257" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="265" t="s">
+      <c r="BQ7" s="257" t="s">
         <v>86</v>
       </c>
-      <c r="BR7" s="266"/>
-      <c r="BS7" s="266"/>
-      <c r="BT7" s="266"/>
-      <c r="BU7" s="269"/>
+      <c r="BR7" s="255"/>
+      <c r="BS7" s="255"/>
+      <c r="BT7" s="255"/>
+      <c r="BU7" s="290"/>
       <c r="BV7"/>
-      <c r="BW7" s="352"/>
-      <c r="BX7" s="259"/>
-      <c r="BY7" s="260"/>
-      <c r="BZ7" s="260"/>
-      <c r="CA7" s="261"/>
-      <c r="CB7" s="356"/>
-      <c r="CC7" s="354"/>
-      <c r="CD7" s="354"/>
+      <c r="BW7" s="318"/>
+      <c r="BX7" s="283"/>
+      <c r="BY7" s="284"/>
+      <c r="BZ7" s="284"/>
+      <c r="CA7" s="285"/>
+      <c r="CB7" s="314"/>
+      <c r="CC7" s="316"/>
+      <c r="CD7" s="316"/>
       <c r="CH7" s="142"/>
       <c r="CI7" s="143"/>
     </row>
     <row r="8" spans="1:87" s="144" customFormat="1">
-      <c r="A8" s="301"/>
-      <c r="B8" s="304"/>
+      <c r="A8" s="265"/>
+      <c r="B8" s="268"/>
       <c r="C8" s="247"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="307"/>
+      <c r="D8" s="260"/>
+      <c r="E8" s="260"/>
       <c r="F8" s="247"/>
       <c r="G8" s="247"/>
-      <c r="H8" s="325"/>
-      <c r="I8" s="325"/>
+      <c r="H8" s="299"/>
+      <c r="I8" s="299"/>
       <c r="J8" s="247"/>
-      <c r="K8" s="328"/>
-      <c r="L8" s="328"/>
-      <c r="M8" s="328"/>
-      <c r="N8" s="328"/>
-      <c r="O8" s="328"/>
-      <c r="P8" s="328"/>
-      <c r="Q8" s="328"/>
-      <c r="R8" s="328"/>
-      <c r="S8" s="328"/>
-      <c r="T8" s="328"/>
-      <c r="U8" s="328"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="308"/>
+      <c r="P8" s="308"/>
+      <c r="Q8" s="308"/>
+      <c r="R8" s="308"/>
+      <c r="S8" s="308"/>
+      <c r="T8" s="308"/>
+      <c r="U8" s="308"/>
       <c r="V8" s="145" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="328"/>
+      <c r="X8" s="308"/>
       <c r="Y8" s="247"/>
       <c r="Z8" s="247"/>
       <c r="AA8" s="247"/>
       <c r="AB8" s="247"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
+      <c r="AC8" s="299"/>
+      <c r="AD8" s="299"/>
+      <c r="AE8" s="299"/>
+      <c r="AF8" s="299"/>
       <c r="AG8" s="247"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
+      <c r="AH8" s="299"/>
+      <c r="AI8" s="299"/>
       <c r="AJ8" s="247"/>
       <c r="AK8" s="247"/>
       <c r="AL8" s="247"/>
       <c r="AM8" s="247"/>
-      <c r="AN8" s="319"/>
+      <c r="AN8" s="254"/>
       <c r="AO8" s="247"/>
       <c r="AP8" s="247"/>
       <c r="AQ8" s="247"/>
@@ -11835,28 +12274,28 @@
       <c r="BA8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="267"/>
-      <c r="BC8" s="249"/>
-      <c r="BD8" s="249"/>
-      <c r="BE8" s="274"/>
-      <c r="BF8" s="249"/>
-      <c r="BG8" s="249"/>
-      <c r="BH8" s="249"/>
-      <c r="BI8" s="249"/>
-      <c r="BJ8" s="249"/>
-      <c r="BK8" s="249"/>
-      <c r="BL8" s="312"/>
-      <c r="BM8" s="249"/>
-      <c r="BN8" s="267"/>
-      <c r="BO8" s="249"/>
-      <c r="BP8" s="267"/>
-      <c r="BQ8" s="267"/>
-      <c r="BR8" s="267"/>
-      <c r="BS8" s="267"/>
-      <c r="BT8" s="267"/>
-      <c r="BU8" s="270"/>
+      <c r="BB8" s="256"/>
+      <c r="BC8" s="241"/>
+      <c r="BD8" s="241"/>
+      <c r="BE8" s="293"/>
+      <c r="BF8" s="241"/>
+      <c r="BG8" s="241"/>
+      <c r="BH8" s="241"/>
+      <c r="BI8" s="241"/>
+      <c r="BJ8" s="241"/>
+      <c r="BK8" s="241"/>
+      <c r="BL8" s="270"/>
+      <c r="BM8" s="241"/>
+      <c r="BN8" s="256"/>
+      <c r="BO8" s="241"/>
+      <c r="BP8" s="256"/>
+      <c r="BQ8" s="256"/>
+      <c r="BR8" s="256"/>
+      <c r="BS8" s="256"/>
+      <c r="BT8" s="256"/>
+      <c r="BU8" s="291"/>
       <c r="BV8"/>
-      <c r="BW8" s="251"/>
+      <c r="BW8" s="275"/>
       <c r="BX8" s="72" t="s">
         <v>92</v>
       </c>
@@ -11869,9 +12308,9 @@
       <c r="CA8" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="263"/>
-      <c r="CC8" s="243"/>
-      <c r="CD8" s="243"/>
+      <c r="CB8" s="287"/>
+      <c r="CC8" s="272"/>
+      <c r="CD8" s="272"/>
       <c r="CE8" s="141"/>
       <c r="CF8" s="146"/>
       <c r="CH8" s="142"/>
@@ -14495,6 +14934,72 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="A5:A8"/>
@@ -14511,84 +15016,18 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BO7:BO8"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:B16 B1:B9 C9:BU9 B20:B1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B9 D10:F10 J10:BK10 BM10:BU10 C9:BU9 B20:B1048576 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="17" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
     <cfRule type="duplicateValues" dxfId="16" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL10">
     <cfRule type="duplicateValues" dxfId="13" priority="4"/>
@@ -14614,7 +15053,7 @@
     <col min="1" max="1" width="5.5" style="61" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="66" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="68" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="13.83203125" style="68" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="5.5" style="68" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="5.5" style="69" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6640625" style="64" bestFit="1" customWidth="1"/>
@@ -14627,8 +15066,7 @@
     <col min="50" max="50" width="6.6640625" style="63" customWidth="1"/>
     <col min="51" max="53" width="10.5" style="63" customWidth="1" outlineLevel="1"/>
     <col min="54" max="71" width="10.5" style="63" customWidth="1"/>
-    <col min="72" max="72" width="12.5" style="63" customWidth="1"/>
-    <col min="73" max="73" width="12.5" style="63" hidden="1" customWidth="1"/>
+    <col min="72" max="73" width="12.5" style="63" customWidth="1"/>
     <col min="74" max="74" width="12.5" style="122" customWidth="1"/>
     <col min="75" max="79" width="12.6640625" style="64" customWidth="1" outlineLevel="1"/>
     <col min="80" max="80" width="12.6640625" style="65" customWidth="1" outlineLevel="1"/>
@@ -14806,91 +15244,91 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="316" t="str">
+      <c r="A3" s="251" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
-        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2025</v>
-      </c>
-      <c r="B3" s="316"/>
-      <c r="C3" s="316"/>
-      <c r="D3" s="316"/>
-      <c r="E3" s="316"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="316"/>
-      <c r="K3" s="316"/>
-      <c r="L3" s="316"/>
-      <c r="M3" s="316"/>
-      <c r="N3" s="316"/>
-      <c r="O3" s="316"/>
-      <c r="P3" s="316"/>
-      <c r="Q3" s="316"/>
-      <c r="R3" s="316"/>
-      <c r="S3" s="316"/>
-      <c r="T3" s="316"/>
-      <c r="U3" s="316"/>
-      <c r="V3" s="316"/>
-      <c r="W3" s="316"/>
-      <c r="X3" s="316"/>
-      <c r="Y3" s="316"/>
-      <c r="Z3" s="316"/>
-      <c r="AA3" s="316"/>
-      <c r="AB3" s="316"/>
-      <c r="AC3" s="316"/>
-      <c r="AD3" s="316"/>
-      <c r="AE3" s="316"/>
-      <c r="AF3" s="316"/>
-      <c r="AG3" s="316"/>
-      <c r="AH3" s="316"/>
-      <c r="AI3" s="316"/>
-      <c r="AJ3" s="316"/>
-      <c r="AK3" s="316"/>
-      <c r="AL3" s="316"/>
-      <c r="AM3" s="316"/>
-      <c r="AN3" s="316"/>
-      <c r="AO3" s="316"/>
-      <c r="AP3" s="316"/>
-      <c r="AQ3" s="316"/>
-      <c r="AR3" s="316"/>
-      <c r="AS3" s="316"/>
-      <c r="AT3" s="316"/>
-      <c r="AU3" s="316"/>
-      <c r="AV3" s="316"/>
-      <c r="AW3" s="316"/>
-      <c r="AX3" s="316"/>
-      <c r="AY3" s="316"/>
-      <c r="AZ3" s="316"/>
-      <c r="BA3" s="316"/>
-      <c r="BB3" s="316"/>
-      <c r="BC3" s="316"/>
-      <c r="BD3" s="316"/>
-      <c r="BE3" s="316"/>
-      <c r="BF3" s="316"/>
-      <c r="BG3" s="316"/>
-      <c r="BH3" s="316"/>
-      <c r="BI3" s="316"/>
-      <c r="BJ3" s="316"/>
-      <c r="BK3" s="316"/>
-      <c r="BL3" s="316"/>
-      <c r="BM3" s="316"/>
-      <c r="BN3" s="316"/>
-      <c r="BO3" s="316"/>
-      <c r="BP3" s="316"/>
-      <c r="BQ3" s="316"/>
-      <c r="BR3" s="316"/>
-      <c r="BS3" s="316"/>
-      <c r="BT3" s="316"/>
-      <c r="BU3" s="316"/>
+        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
+      </c>
+      <c r="B3" s="251"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="251"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
+      <c r="M3" s="251"/>
+      <c r="N3" s="251"/>
+      <c r="O3" s="251"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
+      <c r="AA3" s="251"/>
+      <c r="AB3" s="251"/>
+      <c r="AC3" s="251"/>
+      <c r="AD3" s="251"/>
+      <c r="AE3" s="251"/>
+      <c r="AF3" s="251"/>
+      <c r="AG3" s="251"/>
+      <c r="AH3" s="251"/>
+      <c r="AI3" s="251"/>
+      <c r="AJ3" s="251"/>
+      <c r="AK3" s="251"/>
+      <c r="AL3" s="251"/>
+      <c r="AM3" s="251"/>
+      <c r="AN3" s="251"/>
+      <c r="AO3" s="251"/>
+      <c r="AP3" s="251"/>
+      <c r="AQ3" s="251"/>
+      <c r="AR3" s="251"/>
+      <c r="AS3" s="251"/>
+      <c r="AT3" s="251"/>
+      <c r="AU3" s="251"/>
+      <c r="AV3" s="251"/>
+      <c r="AW3" s="251"/>
+      <c r="AX3" s="251"/>
+      <c r="AY3" s="251"/>
+      <c r="AZ3" s="251"/>
+      <c r="BA3" s="251"/>
+      <c r="BB3" s="251"/>
+      <c r="BC3" s="251"/>
+      <c r="BD3" s="251"/>
+      <c r="BE3" s="251"/>
+      <c r="BF3" s="251"/>
+      <c r="BG3" s="251"/>
+      <c r="BH3" s="251"/>
+      <c r="BI3" s="251"/>
+      <c r="BJ3" s="251"/>
+      <c r="BK3" s="251"/>
+      <c r="BL3" s="251"/>
+      <c r="BM3" s="251"/>
+      <c r="BN3" s="251"/>
+      <c r="BO3" s="251"/>
+      <c r="BP3" s="251"/>
+      <c r="BQ3" s="251"/>
+      <c r="BR3" s="251"/>
+      <c r="BS3" s="251"/>
+      <c r="BT3" s="251"/>
+      <c r="BU3" s="251"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="297" t="s">
+      <c r="BW3" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="297"/>
-      <c r="BY3" s="297"/>
-      <c r="BZ3" s="297"/>
-      <c r="CA3" s="297"/>
-      <c r="CB3" s="298"/>
+      <c r="BX3" s="261"/>
+      <c r="BY3" s="261"/>
+      <c r="BZ3" s="261"/>
+      <c r="CA3" s="261"/>
+      <c r="CB3" s="262"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -14900,7 +15338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:87" s="16" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="4" spans="1:87" s="16" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -14974,16 +15412,16 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="298"/>
-      <c r="BX4" s="298"/>
-      <c r="BY4" s="298"/>
-      <c r="BZ4" s="298"/>
-      <c r="CA4" s="298"/>
-      <c r="CB4" s="298"/>
+      <c r="BW4" s="262"/>
+      <c r="BX4" s="262"/>
+      <c r="BY4" s="262"/>
+      <c r="BZ4" s="262"/>
+      <c r="CA4" s="262"/>
+      <c r="CB4" s="262"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
-    <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -15057,16 +15495,16 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="298"/>
-      <c r="BX5" s="298"/>
-      <c r="BY5" s="298"/>
-      <c r="BZ5" s="298"/>
-      <c r="CA5" s="298"/>
-      <c r="CB5" s="298"/>
+      <c r="BW5" s="262"/>
+      <c r="BX5" s="262"/>
+      <c r="BY5" s="262"/>
+      <c r="BZ5" s="262"/>
+      <c r="CA5" s="262"/>
+      <c r="CB5" s="262"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
-    <row r="6" spans="1:87" s="14" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="6" spans="1:87" s="14" customFormat="1" ht="18.75" customHeight="1" outlineLevel="1">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -15140,16 +15578,16 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="297"/>
-      <c r="BX6" s="297"/>
-      <c r="BY6" s="297"/>
-      <c r="BZ6" s="297"/>
-      <c r="CA6" s="297"/>
-      <c r="CB6" s="298"/>
+      <c r="BW6" s="261"/>
+      <c r="BX6" s="261"/>
+      <c r="BY6" s="261"/>
+      <c r="BZ6" s="261"/>
+      <c r="CA6" s="261"/>
+      <c r="CB6" s="262"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
-    <row r="7" spans="1:87" s="14" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="7" spans="1:87" s="14" customFormat="1" ht="12.75" customHeight="1" outlineLevel="1">
       <c r="A7" s="21"/>
       <c r="B7" s="22"/>
       <c r="C7" s="21"/>
@@ -15232,535 +15670,535 @@
       <c r="CC7" s="25"/>
       <c r="CD7" s="25"/>
     </row>
-    <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="299" t="s">
+    <row r="8" spans="1:87" s="364" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="349" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="302" t="s">
+      <c r="B8" s="350" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="245" t="s">
+      <c r="C8" s="344" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="305" t="s">
+      <c r="D8" s="351" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="305" t="s">
+      <c r="E8" s="351" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="340" t="s">
         <v>127</v>
       </c>
-      <c r="G8" s="308" t="s">
+      <c r="G8" s="352" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="276" t="s">
+      <c r="H8" s="352" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="276" t="s">
+      <c r="I8" s="352" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="308" t="s">
+      <c r="J8" s="352" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="279" t="s">
+      <c r="K8" s="353" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="280"/>
-      <c r="P8" s="280"/>
-      <c r="Q8" s="280"/>
-      <c r="R8" s="280"/>
-      <c r="S8" s="280"/>
-      <c r="T8" s="280"/>
-      <c r="U8" s="280"/>
-      <c r="V8" s="280"/>
-      <c r="W8" s="280"/>
-      <c r="X8" s="280"/>
-      <c r="Y8" s="281" t="s">
+      <c r="L8" s="354"/>
+      <c r="M8" s="354"/>
+      <c r="N8" s="354"/>
+      <c r="O8" s="354"/>
+      <c r="P8" s="354"/>
+      <c r="Q8" s="354"/>
+      <c r="R8" s="354"/>
+      <c r="S8" s="354"/>
+      <c r="T8" s="354"/>
+      <c r="U8" s="354"/>
+      <c r="V8" s="354"/>
+      <c r="W8" s="354"/>
+      <c r="X8" s="354"/>
+      <c r="Y8" s="355" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="282"/>
-      <c r="AA8" s="282"/>
-      <c r="AB8" s="282"/>
-      <c r="AC8" s="282"/>
-      <c r="AD8" s="282"/>
-      <c r="AE8" s="282"/>
-      <c r="AF8" s="282"/>
-      <c r="AG8" s="282"/>
-      <c r="AH8" s="282"/>
-      <c r="AI8" s="282"/>
-      <c r="AJ8" s="282"/>
-      <c r="AK8" s="282"/>
-      <c r="AL8" s="282"/>
-      <c r="AM8" s="282"/>
-      <c r="AN8" s="282"/>
-      <c r="AO8" s="283"/>
-      <c r="AP8" s="308" t="s">
+      <c r="Z8" s="356"/>
+      <c r="AA8" s="356"/>
+      <c r="AB8" s="356"/>
+      <c r="AC8" s="356"/>
+      <c r="AD8" s="356"/>
+      <c r="AE8" s="356"/>
+      <c r="AF8" s="356"/>
+      <c r="AG8" s="356"/>
+      <c r="AH8" s="356"/>
+      <c r="AI8" s="356"/>
+      <c r="AJ8" s="356"/>
+      <c r="AK8" s="356"/>
+      <c r="AL8" s="356"/>
+      <c r="AM8" s="356"/>
+      <c r="AN8" s="356"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="352" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="308" t="s">
+      <c r="AQ8" s="352" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="308" t="s">
+      <c r="AR8" s="352" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="308" t="s">
+      <c r="AS8" s="352" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="308" t="s">
+      <c r="AT8" s="352" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="308" t="s">
+      <c r="AU8" s="352" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="245" t="s">
+      <c r="AV8" s="344" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="245" t="s">
+      <c r="AW8" s="344" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="245" t="s">
+      <c r="AX8" s="344" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="313" t="s">
+      <c r="AY8" s="358" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="314"/>
-      <c r="BA8" s="314"/>
-      <c r="BB8" s="314"/>
-      <c r="BC8" s="314"/>
-      <c r="BD8" s="314"/>
-      <c r="BE8" s="314"/>
-      <c r="BF8" s="314"/>
-      <c r="BG8" s="314"/>
-      <c r="BH8" s="314"/>
-      <c r="BI8" s="314"/>
-      <c r="BJ8" s="314"/>
-      <c r="BK8" s="314"/>
-      <c r="BL8" s="314"/>
-      <c r="BM8" s="314"/>
-      <c r="BN8" s="314"/>
-      <c r="BO8" s="314"/>
-      <c r="BP8" s="315"/>
-      <c r="BQ8" s="268" t="s">
+      <c r="AZ8" s="359"/>
+      <c r="BA8" s="359"/>
+      <c r="BB8" s="359"/>
+      <c r="BC8" s="359"/>
+      <c r="BD8" s="359"/>
+      <c r="BE8" s="359"/>
+      <c r="BF8" s="359"/>
+      <c r="BG8" s="359"/>
+      <c r="BH8" s="359"/>
+      <c r="BI8" s="359"/>
+      <c r="BJ8" s="359"/>
+      <c r="BK8" s="359"/>
+      <c r="BL8" s="359"/>
+      <c r="BM8" s="359"/>
+      <c r="BN8" s="359"/>
+      <c r="BO8" s="359"/>
+      <c r="BP8" s="360"/>
+      <c r="BQ8" s="361" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="275"/>
-      <c r="BS8" s="265" t="s">
+      <c r="BR8" s="362"/>
+      <c r="BS8" s="344" t="s">
         <v>128</v>
       </c>
-      <c r="BT8" s="265" t="s">
+      <c r="BT8" s="344" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="268" t="s">
+      <c r="BU8" s="361" t="s">
         <v>28</v>
       </c>
-      <c r="BV8" s="114"/>
-      <c r="BW8" s="250" t="s">
+      <c r="BV8" s="363"/>
+      <c r="BW8" s="326" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="253" t="s">
+      <c r="BX8" s="327" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="254"/>
-      <c r="BZ8" s="254"/>
-      <c r="CA8" s="255"/>
-      <c r="CB8" s="262" t="s">
+      <c r="BY8" s="328"/>
+      <c r="BZ8" s="328"/>
+      <c r="CA8" s="329"/>
+      <c r="CB8" s="322" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="242" t="s">
+      <c r="CC8" s="322" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="242" t="s">
+      <c r="CD8" s="322" t="s">
         <v>33</v>
       </c>
-      <c r="CH8" s="27"/>
-      <c r="CI8" s="28"/>
+      <c r="CH8" s="341"/>
+      <c r="CI8" s="342"/>
     </row>
-    <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="300"/>
-      <c r="B9" s="303"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="341"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="284" t="s">
+    <row r="9" spans="1:87" s="364" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="365"/>
+      <c r="B9" s="366"/>
+      <c r="C9" s="345"/>
+      <c r="D9" s="367"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="343"/>
+      <c r="G9" s="368"/>
+      <c r="H9" s="368"/>
+      <c r="I9" s="368"/>
+      <c r="J9" s="368"/>
+      <c r="K9" s="369" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="284" t="s">
+      <c r="L9" s="369" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="284" t="s">
+      <c r="M9" s="369" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="284" t="s">
+      <c r="N9" s="369" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="284" t="s">
+      <c r="O9" s="369" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="284" t="s">
+      <c r="P9" s="369" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="284" t="s">
+      <c r="Q9" s="369" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="284" t="s">
+      <c r="R9" s="369" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="284" t="s">
+      <c r="S9" s="369" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="284" t="s">
+      <c r="T9" s="369" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="284" t="s">
+      <c r="U9" s="369" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="293" t="s">
+      <c r="V9" s="370" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="294"/>
-      <c r="X9" s="284" t="s">
+      <c r="W9" s="371"/>
+      <c r="X9" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="287" t="s">
+      <c r="Y9" s="372" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="287" t="s">
+      <c r="Z9" s="372" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="287" t="s">
+      <c r="AA9" s="372" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="287" t="s">
+      <c r="AB9" s="372" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="290" t="s">
+      <c r="AC9" s="372" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="290" t="s">
+      <c r="AD9" s="372" t="s">
         <v>129</v>
       </c>
-      <c r="AE9" s="290" t="s">
+      <c r="AE9" s="372" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="290" t="s">
+      <c r="AF9" s="372" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="287" t="s">
+      <c r="AG9" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="290" t="s">
+      <c r="AH9" s="372" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="290" t="s">
+      <c r="AI9" s="372" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="287" t="s">
+      <c r="AJ9" s="372" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="320" t="s">
+      <c r="AK9" s="361" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="245" t="s">
+      <c r="AL9" s="344" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="287" t="s">
+      <c r="AM9" s="372" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="317" t="s">
+      <c r="AN9" s="344" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="245" t="s">
+      <c r="AO9" s="344" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="309"/>
-      <c r="AQ9" s="309"/>
-      <c r="AR9" s="309"/>
-      <c r="AS9" s="309"/>
-      <c r="AT9" s="309"/>
-      <c r="AU9" s="309"/>
-      <c r="AV9" s="246"/>
-      <c r="AW9" s="246"/>
-      <c r="AX9" s="246"/>
-      <c r="AY9" s="313" t="s">
+      <c r="AP9" s="368"/>
+      <c r="AQ9" s="368"/>
+      <c r="AR9" s="368"/>
+      <c r="AS9" s="368"/>
+      <c r="AT9" s="368"/>
+      <c r="AU9" s="368"/>
+      <c r="AV9" s="345"/>
+      <c r="AW9" s="345"/>
+      <c r="AX9" s="345"/>
+      <c r="AY9" s="358" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="314"/>
-      <c r="BA9" s="314"/>
-      <c r="BB9" s="314"/>
-      <c r="BC9" s="314"/>
-      <c r="BD9" s="314"/>
-      <c r="BE9" s="314"/>
-      <c r="BF9" s="314"/>
-      <c r="BG9" s="314"/>
-      <c r="BH9" s="314"/>
-      <c r="BI9" s="314"/>
-      <c r="BJ9" s="315"/>
-      <c r="BK9" s="313" t="s">
+      <c r="AZ9" s="359"/>
+      <c r="BA9" s="359"/>
+      <c r="BB9" s="359"/>
+      <c r="BC9" s="359"/>
+      <c r="BD9" s="359"/>
+      <c r="BE9" s="359"/>
+      <c r="BF9" s="359"/>
+      <c r="BG9" s="359"/>
+      <c r="BH9" s="359"/>
+      <c r="BI9" s="359"/>
+      <c r="BJ9" s="360"/>
+      <c r="BK9" s="358" t="s">
         <v>65</v>
       </c>
-      <c r="BL9" s="314"/>
-      <c r="BM9" s="314"/>
-      <c r="BN9" s="314"/>
-      <c r="BO9" s="314"/>
-      <c r="BP9" s="315"/>
-      <c r="BQ9" s="266" t="s">
+      <c r="BL9" s="359"/>
+      <c r="BM9" s="359"/>
+      <c r="BN9" s="359"/>
+      <c r="BO9" s="359"/>
+      <c r="BP9" s="360"/>
+      <c r="BQ9" s="345" t="s">
         <v>66</v>
       </c>
-      <c r="BR9" s="266" t="s">
+      <c r="BR9" s="345" t="s">
         <v>67</v>
       </c>
-      <c r="BS9" s="266"/>
-      <c r="BT9" s="266"/>
-      <c r="BU9" s="269"/>
-      <c r="BV9" s="114"/>
-      <c r="BW9" s="251"/>
-      <c r="BX9" s="256"/>
-      <c r="BY9" s="257"/>
-      <c r="BZ9" s="257"/>
-      <c r="CA9" s="258"/>
-      <c r="CB9" s="263"/>
-      <c r="CC9" s="243"/>
-      <c r="CD9" s="243"/>
-      <c r="CH9" s="27"/>
-      <c r="CI9" s="28"/>
+      <c r="BS9" s="345"/>
+      <c r="BT9" s="345"/>
+      <c r="BU9" s="373"/>
+      <c r="BV9" s="363"/>
+      <c r="BW9" s="330"/>
+      <c r="BX9" s="331"/>
+      <c r="BY9" s="332"/>
+      <c r="BZ9" s="332"/>
+      <c r="CA9" s="333"/>
+      <c r="CB9" s="323"/>
+      <c r="CC9" s="323"/>
+      <c r="CD9" s="323"/>
+      <c r="CH9" s="341"/>
+      <c r="CI9" s="342"/>
     </row>
-    <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="300"/>
-      <c r="B10" s="303"/>
-      <c r="C10" s="246"/>
-      <c r="D10" s="306"/>
-      <c r="E10" s="306"/>
-      <c r="F10" s="341"/>
-      <c r="G10" s="309"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="309"/>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
-      <c r="M10" s="285"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
-      <c r="R10" s="285"/>
-      <c r="S10" s="285"/>
-      <c r="T10" s="285"/>
-      <c r="U10" s="285"/>
-      <c r="V10" s="295"/>
-      <c r="W10" s="296"/>
-      <c r="X10" s="285"/>
-      <c r="Y10" s="288"/>
-      <c r="Z10" s="288"/>
-      <c r="AA10" s="288"/>
-      <c r="AB10" s="288"/>
-      <c r="AC10" s="291"/>
-      <c r="AD10" s="291"/>
-      <c r="AE10" s="291"/>
-      <c r="AF10" s="291"/>
-      <c r="AG10" s="288"/>
-      <c r="AH10" s="291"/>
-      <c r="AI10" s="291"/>
-      <c r="AJ10" s="288"/>
-      <c r="AK10" s="321"/>
-      <c r="AL10" s="246"/>
-      <c r="AM10" s="288"/>
-      <c r="AN10" s="318"/>
-      <c r="AO10" s="246"/>
-      <c r="AP10" s="309"/>
-      <c r="AQ10" s="309"/>
-      <c r="AR10" s="309"/>
-      <c r="AS10" s="309"/>
-      <c r="AT10" s="309"/>
-      <c r="AU10" s="309"/>
-      <c r="AV10" s="246"/>
-      <c r="AW10" s="246"/>
-      <c r="AX10" s="246"/>
-      <c r="AY10" s="101" t="s">
+    <row r="10" spans="1:87" s="382" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="365"/>
+      <c r="B10" s="366"/>
+      <c r="C10" s="345"/>
+      <c r="D10" s="367"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="368"/>
+      <c r="H10" s="368"/>
+      <c r="I10" s="368"/>
+      <c r="J10" s="368"/>
+      <c r="K10" s="374"/>
+      <c r="L10" s="374"/>
+      <c r="M10" s="374"/>
+      <c r="N10" s="374"/>
+      <c r="O10" s="374"/>
+      <c r="P10" s="374"/>
+      <c r="Q10" s="374"/>
+      <c r="R10" s="374"/>
+      <c r="S10" s="374"/>
+      <c r="T10" s="374"/>
+      <c r="U10" s="374"/>
+      <c r="V10" s="375"/>
+      <c r="W10" s="376"/>
+      <c r="X10" s="374"/>
+      <c r="Y10" s="377"/>
+      <c r="Z10" s="377"/>
+      <c r="AA10" s="377"/>
+      <c r="AB10" s="377"/>
+      <c r="AC10" s="377"/>
+      <c r="AD10" s="377"/>
+      <c r="AE10" s="377"/>
+      <c r="AF10" s="377"/>
+      <c r="AG10" s="377"/>
+      <c r="AH10" s="377"/>
+      <c r="AI10" s="377"/>
+      <c r="AJ10" s="377"/>
+      <c r="AK10" s="373"/>
+      <c r="AL10" s="345"/>
+      <c r="AM10" s="377"/>
+      <c r="AN10" s="345"/>
+      <c r="AO10" s="345"/>
+      <c r="AP10" s="368"/>
+      <c r="AQ10" s="368"/>
+      <c r="AR10" s="368"/>
+      <c r="AS10" s="368"/>
+      <c r="AT10" s="368"/>
+      <c r="AU10" s="368"/>
+      <c r="AV10" s="345"/>
+      <c r="AW10" s="345"/>
+      <c r="AX10" s="345"/>
+      <c r="AY10" s="378" t="s">
         <v>68</v>
       </c>
-      <c r="AZ10" s="101" t="s">
+      <c r="AZ10" s="378" t="s">
         <v>69</v>
       </c>
-      <c r="BA10" s="101" t="s">
+      <c r="BA10" s="378" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="349" t="s">
+      <c r="BB10" s="379" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="343" t="s">
+      <c r="BC10" s="380" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="343" t="s">
+      <c r="BD10" s="380" t="s">
         <v>73</v>
       </c>
-      <c r="BE10" s="343" t="s">
+      <c r="BE10" s="380" t="s">
         <v>130</v>
       </c>
-      <c r="BF10" s="343" t="s">
+      <c r="BF10" s="380" t="s">
         <v>75</v>
       </c>
-      <c r="BG10" s="343" t="s">
+      <c r="BG10" s="380" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="343" t="s">
+      <c r="BH10" s="380" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="343" t="s">
+      <c r="BI10" s="380" t="s">
         <v>80</v>
       </c>
-      <c r="BJ10" s="347" t="s">
+      <c r="BJ10" s="381" t="s">
         <v>81</v>
       </c>
-      <c r="BK10" s="343" t="s">
+      <c r="BK10" s="380" t="s">
         <v>82</v>
       </c>
-      <c r="BL10" s="345" t="s">
+      <c r="BL10" s="381" t="s">
         <v>83</v>
       </c>
-      <c r="BM10" s="343" t="s">
+      <c r="BM10" s="380" t="s">
         <v>84</v>
       </c>
-      <c r="BN10" s="345" t="s">
+      <c r="BN10" s="381" t="s">
         <v>85</v>
       </c>
-      <c r="BO10" s="345" t="s">
+      <c r="BO10" s="381" t="s">
         <v>131</v>
       </c>
-      <c r="BP10" s="265" t="s">
+      <c r="BP10" s="344" t="s">
         <v>86</v>
       </c>
-      <c r="BQ10" s="266"/>
-      <c r="BR10" s="266"/>
-      <c r="BS10" s="266"/>
-      <c r="BT10" s="266"/>
-      <c r="BU10" s="269"/>
-      <c r="BV10" s="114"/>
-      <c r="BW10" s="252"/>
-      <c r="BX10" s="259"/>
-      <c r="BY10" s="260"/>
-      <c r="BZ10" s="260"/>
-      <c r="CA10" s="261"/>
-      <c r="CB10" s="264"/>
-      <c r="CC10" s="244"/>
-      <c r="CD10" s="244"/>
-      <c r="CH10" s="27"/>
-      <c r="CI10" s="28"/>
+      <c r="BQ10" s="345"/>
+      <c r="BR10" s="345"/>
+      <c r="BS10" s="345"/>
+      <c r="BT10" s="345"/>
+      <c r="BU10" s="373"/>
+      <c r="BV10" s="363"/>
+      <c r="BW10" s="334"/>
+      <c r="BX10" s="335"/>
+      <c r="BY10" s="336"/>
+      <c r="BZ10" s="336"/>
+      <c r="CA10" s="337"/>
+      <c r="CB10" s="324"/>
+      <c r="CC10" s="324"/>
+      <c r="CD10" s="324"/>
+      <c r="CH10" s="341"/>
+      <c r="CI10" s="342"/>
     </row>
-    <row r="11" spans="1:87" s="29" customFormat="1" ht="28">
-      <c r="A11" s="301"/>
-      <c r="B11" s="304"/>
-      <c r="C11" s="247"/>
-      <c r="D11" s="307"/>
-      <c r="E11" s="307"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="278"/>
-      <c r="I11" s="278"/>
-      <c r="J11" s="310"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286"/>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="286"/>
-      <c r="Q11" s="286"/>
-      <c r="R11" s="286"/>
-      <c r="S11" s="286"/>
-      <c r="T11" s="286"/>
-      <c r="U11" s="286"/>
-      <c r="V11" s="30" t="s">
+    <row r="11" spans="1:87" s="382" customFormat="1" ht="28">
+      <c r="A11" s="383"/>
+      <c r="B11" s="384"/>
+      <c r="C11" s="348"/>
+      <c r="D11" s="385"/>
+      <c r="E11" s="385"/>
+      <c r="F11" s="346"/>
+      <c r="G11" s="386"/>
+      <c r="H11" s="386"/>
+      <c r="I11" s="386"/>
+      <c r="J11" s="386"/>
+      <c r="K11" s="387"/>
+      <c r="L11" s="387"/>
+      <c r="M11" s="387"/>
+      <c r="N11" s="387"/>
+      <c r="O11" s="387"/>
+      <c r="P11" s="387"/>
+      <c r="Q11" s="387"/>
+      <c r="R11" s="387"/>
+      <c r="S11" s="387"/>
+      <c r="T11" s="387"/>
+      <c r="U11" s="387"/>
+      <c r="V11" s="347" t="s">
         <v>87</v>
       </c>
-      <c r="W11" s="30" t="s">
+      <c r="W11" s="347" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="286"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="292"/>
-      <c r="AD11" s="292"/>
-      <c r="AE11" s="292"/>
-      <c r="AF11" s="292"/>
-      <c r="AG11" s="289"/>
-      <c r="AH11" s="292"/>
-      <c r="AI11" s="292"/>
-      <c r="AJ11" s="289"/>
-      <c r="AK11" s="322"/>
-      <c r="AL11" s="247"/>
-      <c r="AM11" s="289"/>
-      <c r="AN11" s="319"/>
-      <c r="AO11" s="247"/>
-      <c r="AP11" s="310"/>
-      <c r="AQ11" s="310"/>
-      <c r="AR11" s="310"/>
-      <c r="AS11" s="310"/>
-      <c r="AT11" s="310"/>
-      <c r="AU11" s="310"/>
-      <c r="AV11" s="247"/>
-      <c r="AW11" s="247"/>
-      <c r="AX11" s="247"/>
-      <c r="AY11" s="102" t="s">
+      <c r="X11" s="387"/>
+      <c r="Y11" s="388"/>
+      <c r="Z11" s="388"/>
+      <c r="AA11" s="388"/>
+      <c r="AB11" s="388"/>
+      <c r="AC11" s="388"/>
+      <c r="AD11" s="388"/>
+      <c r="AE11" s="388"/>
+      <c r="AF11" s="388"/>
+      <c r="AG11" s="388"/>
+      <c r="AH11" s="388"/>
+      <c r="AI11" s="388"/>
+      <c r="AJ11" s="388"/>
+      <c r="AK11" s="389"/>
+      <c r="AL11" s="348"/>
+      <c r="AM11" s="388"/>
+      <c r="AN11" s="348"/>
+      <c r="AO11" s="348"/>
+      <c r="AP11" s="386"/>
+      <c r="AQ11" s="386"/>
+      <c r="AR11" s="386"/>
+      <c r="AS11" s="386"/>
+      <c r="AT11" s="386"/>
+      <c r="AU11" s="386"/>
+      <c r="AV11" s="348"/>
+      <c r="AW11" s="348"/>
+      <c r="AX11" s="348"/>
+      <c r="AY11" s="390" t="s">
         <v>89</v>
       </c>
-      <c r="AZ11" s="102" t="s">
+      <c r="AZ11" s="390" t="s">
         <v>90</v>
       </c>
-      <c r="BA11" s="102" t="s">
+      <c r="BA11" s="390" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="350"/>
-      <c r="BC11" s="344"/>
-      <c r="BD11" s="344"/>
-      <c r="BE11" s="344"/>
-      <c r="BF11" s="344"/>
-      <c r="BG11" s="344"/>
-      <c r="BH11" s="344"/>
-      <c r="BI11" s="344"/>
-      <c r="BJ11" s="348"/>
-      <c r="BK11" s="344"/>
-      <c r="BL11" s="346"/>
-      <c r="BM11" s="344"/>
-      <c r="BN11" s="346"/>
-      <c r="BO11" s="346"/>
-      <c r="BP11" s="267"/>
-      <c r="BQ11" s="267"/>
-      <c r="BR11" s="267"/>
-      <c r="BS11" s="267"/>
-      <c r="BT11" s="267"/>
-      <c r="BU11" s="270"/>
-      <c r="BV11" s="114"/>
-      <c r="BW11" s="252"/>
-      <c r="BX11" s="72" t="s">
+      <c r="BB11" s="391"/>
+      <c r="BC11" s="392"/>
+      <c r="BD11" s="392"/>
+      <c r="BE11" s="392"/>
+      <c r="BF11" s="392"/>
+      <c r="BG11" s="392"/>
+      <c r="BH11" s="392"/>
+      <c r="BI11" s="392"/>
+      <c r="BJ11" s="393"/>
+      <c r="BK11" s="392"/>
+      <c r="BL11" s="393"/>
+      <c r="BM11" s="392"/>
+      <c r="BN11" s="393"/>
+      <c r="BO11" s="393"/>
+      <c r="BP11" s="348"/>
+      <c r="BQ11" s="348"/>
+      <c r="BR11" s="348"/>
+      <c r="BS11" s="348"/>
+      <c r="BT11" s="348"/>
+      <c r="BU11" s="389"/>
+      <c r="BV11" s="363"/>
+      <c r="BW11" s="334"/>
+      <c r="BX11" s="338" t="s">
         <v>92</v>
       </c>
-      <c r="BY11" s="72" t="s">
+      <c r="BY11" s="338" t="s">
         <v>93</v>
       </c>
-      <c r="BZ11" s="72" t="s">
+      <c r="BZ11" s="338" t="s">
         <v>94</v>
       </c>
-      <c r="CA11" s="73" t="s">
+      <c r="CA11" s="339" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="264"/>
-      <c r="CC11" s="244"/>
-      <c r="CD11" s="244"/>
-      <c r="CE11" s="11"/>
-      <c r="CF11" s="31"/>
-      <c r="CH11" s="27"/>
-      <c r="CI11" s="28"/>
+      <c r="CB11" s="324"/>
+      <c r="CC11" s="324"/>
+      <c r="CD11" s="324"/>
+      <c r="CE11" s="364"/>
+      <c r="CF11" s="394"/>
+      <c r="CH11" s="341"/>
+      <c r="CI11" s="342"/>
     </row>
     <row r="12" spans="1:87" s="34" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="32">
@@ -18155,32 +18593,40 @@
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="T9:T11"/>
     <mergeCell ref="BX8:CA10"/>
     <mergeCell ref="CB8:CB11"/>
     <mergeCell ref="CC8:CC11"/>
@@ -18197,46 +18643,38 @@
     <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="BU8:BU11"/>
     <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="AO9:AO11"/>
     <mergeCell ref="AR8:AR11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="Q9:Q11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 C12:BU12 B22:B1048576">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18470,91 +18908,91 @@
       <c r="CD2" s="137"/>
     </row>
     <row r="3" spans="1:87" s="139" customFormat="1" outlineLevel="1">
-      <c r="A3" s="333" t="str">
+      <c r="A3" s="295" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
-        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2025</v>
-      </c>
-      <c r="B3" s="333"/>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333"/>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
-      <c r="I3" s="333"/>
-      <c r="J3" s="333"/>
-      <c r="K3" s="333"/>
-      <c r="L3" s="333"/>
-      <c r="M3" s="333"/>
-      <c r="N3" s="333"/>
-      <c r="O3" s="333"/>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
-      <c r="Y3" s="333"/>
-      <c r="Z3" s="333"/>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333"/>
-      <c r="AE3" s="333"/>
-      <c r="AF3" s="333"/>
-      <c r="AG3" s="333"/>
-      <c r="AH3" s="333"/>
-      <c r="AI3" s="333"/>
-      <c r="AJ3" s="333"/>
-      <c r="AK3" s="333"/>
-      <c r="AL3" s="333"/>
-      <c r="AM3" s="333"/>
-      <c r="AN3" s="333"/>
-      <c r="AO3" s="333"/>
-      <c r="AP3" s="333"/>
-      <c r="AQ3" s="333"/>
-      <c r="AR3" s="333"/>
-      <c r="AS3" s="333"/>
-      <c r="AT3" s="333"/>
-      <c r="AU3" s="333"/>
-      <c r="AV3" s="333"/>
-      <c r="AW3" s="333"/>
-      <c r="AX3" s="333"/>
-      <c r="AY3" s="333"/>
-      <c r="AZ3" s="333"/>
-      <c r="BA3" s="333"/>
-      <c r="BB3" s="333"/>
-      <c r="BC3" s="333"/>
-      <c r="BD3" s="333"/>
-      <c r="BE3" s="333"/>
-      <c r="BF3" s="333"/>
-      <c r="BG3" s="333"/>
-      <c r="BH3" s="333"/>
-      <c r="BI3" s="333"/>
-      <c r="BJ3" s="333"/>
-      <c r="BK3" s="333"/>
-      <c r="BL3" s="333"/>
-      <c r="BM3" s="333"/>
-      <c r="BN3" s="333"/>
-      <c r="BO3" s="333"/>
-      <c r="BP3" s="333"/>
-      <c r="BQ3" s="333"/>
-      <c r="BR3" s="333"/>
-      <c r="BS3" s="333"/>
-      <c r="BT3" s="333"/>
-      <c r="BU3" s="333"/>
+        <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
+      </c>
+      <c r="B3" s="295"/>
+      <c r="C3" s="295"/>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="295"/>
+      <c r="K3" s="295"/>
+      <c r="L3" s="295"/>
+      <c r="M3" s="295"/>
+      <c r="N3" s="295"/>
+      <c r="O3" s="295"/>
+      <c r="P3" s="295"/>
+      <c r="Q3" s="295"/>
+      <c r="R3" s="295"/>
+      <c r="S3" s="295"/>
+      <c r="T3" s="295"/>
+      <c r="U3" s="295"/>
+      <c r="V3" s="295"/>
+      <c r="W3" s="295"/>
+      <c r="X3" s="295"/>
+      <c r="Y3" s="295"/>
+      <c r="Z3" s="295"/>
+      <c r="AA3" s="295"/>
+      <c r="AB3" s="295"/>
+      <c r="AC3" s="295"/>
+      <c r="AD3" s="295"/>
+      <c r="AE3" s="295"/>
+      <c r="AF3" s="295"/>
+      <c r="AG3" s="295"/>
+      <c r="AH3" s="295"/>
+      <c r="AI3" s="295"/>
+      <c r="AJ3" s="295"/>
+      <c r="AK3" s="295"/>
+      <c r="AL3" s="295"/>
+      <c r="AM3" s="295"/>
+      <c r="AN3" s="295"/>
+      <c r="AO3" s="295"/>
+      <c r="AP3" s="295"/>
+      <c r="AQ3" s="295"/>
+      <c r="AR3" s="295"/>
+      <c r="AS3" s="295"/>
+      <c r="AT3" s="295"/>
+      <c r="AU3" s="295"/>
+      <c r="AV3" s="295"/>
+      <c r="AW3" s="295"/>
+      <c r="AX3" s="295"/>
+      <c r="AY3" s="295"/>
+      <c r="AZ3" s="295"/>
+      <c r="BA3" s="295"/>
+      <c r="BB3" s="295"/>
+      <c r="BC3" s="295"/>
+      <c r="BD3" s="295"/>
+      <c r="BE3" s="295"/>
+      <c r="BF3" s="295"/>
+      <c r="BG3" s="295"/>
+      <c r="BH3" s="295"/>
+      <c r="BI3" s="295"/>
+      <c r="BJ3" s="295"/>
+      <c r="BK3" s="295"/>
+      <c r="BL3" s="295"/>
+      <c r="BM3" s="295"/>
+      <c r="BN3" s="295"/>
+      <c r="BO3" s="295"/>
+      <c r="BP3" s="295"/>
+      <c r="BQ3" s="295"/>
+      <c r="BR3" s="295"/>
+      <c r="BS3" s="295"/>
+      <c r="BT3" s="295"/>
+      <c r="BU3" s="295"/>
       <c r="BV3"/>
-      <c r="BW3" s="334" t="s">
+      <c r="BW3" s="296" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="334"/>
-      <c r="BY3" s="334"/>
-      <c r="BZ3" s="334"/>
-      <c r="CA3" s="334"/>
-      <c r="CB3" s="333"/>
+      <c r="BX3" s="296"/>
+      <c r="BY3" s="296"/>
+      <c r="BZ3" s="296"/>
+      <c r="CA3" s="296"/>
+      <c r="CB3" s="295"/>
       <c r="CC3" s="138"/>
       <c r="CD3" s="138"/>
       <c r="CE3" s="139" t="s">
@@ -18638,81 +19076,81 @@
       <c r="BT4" s="140"/>
       <c r="BU4" s="140"/>
       <c r="BV4"/>
-      <c r="BW4" s="333"/>
-      <c r="BX4" s="333"/>
-      <c r="BY4" s="333"/>
-      <c r="BZ4" s="333"/>
-      <c r="CA4" s="333"/>
-      <c r="CB4" s="333"/>
+      <c r="BW4" s="295"/>
+      <c r="BX4" s="295"/>
+      <c r="BY4" s="295"/>
+      <c r="BZ4" s="295"/>
+      <c r="CA4" s="295"/>
+      <c r="CB4" s="295"/>
       <c r="CC4" s="138"/>
       <c r="CD4" s="138"/>
     </row>
     <row r="5" spans="1:87" s="141" customFormat="1">
-      <c r="A5" s="299" t="s">
+      <c r="A5" s="263" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="302" t="s">
+      <c r="B5" s="266" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="305" t="s">
+      <c r="D5" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="305" t="s">
+      <c r="E5" s="258" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="340" t="s">
+      <c r="F5" s="319" t="s">
         <v>127</v>
       </c>
       <c r="G5" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="323" t="s">
+      <c r="H5" s="297" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="323" t="s">
+      <c r="I5" s="297" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="245" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="335" t="s">
+      <c r="K5" s="300" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="336"/>
-      <c r="M5" s="336"/>
-      <c r="N5" s="336"/>
-      <c r="O5" s="336"/>
-      <c r="P5" s="336"/>
-      <c r="Q5" s="336"/>
-      <c r="R5" s="336"/>
-      <c r="S5" s="336"/>
-      <c r="T5" s="336"/>
-      <c r="U5" s="336"/>
-      <c r="V5" s="336"/>
-      <c r="W5" s="336"/>
-      <c r="X5" s="336"/>
-      <c r="Y5" s="337" t="s">
+      <c r="L5" s="301"/>
+      <c r="M5" s="301"/>
+      <c r="N5" s="301"/>
+      <c r="O5" s="301"/>
+      <c r="P5" s="301"/>
+      <c r="Q5" s="301"/>
+      <c r="R5" s="301"/>
+      <c r="S5" s="301"/>
+      <c r="T5" s="301"/>
+      <c r="U5" s="301"/>
+      <c r="V5" s="301"/>
+      <c r="W5" s="301"/>
+      <c r="X5" s="301"/>
+      <c r="Y5" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="338"/>
-      <c r="AA5" s="338"/>
-      <c r="AB5" s="338"/>
-      <c r="AC5" s="338"/>
-      <c r="AD5" s="338"/>
-      <c r="AE5" s="338"/>
-      <c r="AF5" s="338"/>
-      <c r="AG5" s="338"/>
-      <c r="AH5" s="338"/>
-      <c r="AI5" s="338"/>
-      <c r="AJ5" s="338"/>
-      <c r="AK5" s="338"/>
-      <c r="AL5" s="338"/>
-      <c r="AM5" s="338"/>
-      <c r="AN5" s="338"/>
-      <c r="AO5" s="339"/>
+      <c r="Z5" s="304"/>
+      <c r="AA5" s="304"/>
+      <c r="AB5" s="304"/>
+      <c r="AC5" s="304"/>
+      <c r="AD5" s="304"/>
+      <c r="AE5" s="304"/>
+      <c r="AF5" s="304"/>
+      <c r="AG5" s="304"/>
+      <c r="AH5" s="304"/>
+      <c r="AI5" s="304"/>
+      <c r="AJ5" s="304"/>
+      <c r="AK5" s="304"/>
+      <c r="AL5" s="304"/>
+      <c r="AM5" s="304"/>
+      <c r="AN5" s="304"/>
+      <c r="AO5" s="305"/>
       <c r="AP5" s="245" t="s">
         <v>16</v>
       </c>
@@ -18740,110 +19178,110 @@
       <c r="AX5" s="245" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="313" t="s">
+      <c r="AY5" s="248" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="314"/>
-      <c r="BA5" s="314"/>
-      <c r="BB5" s="314"/>
-      <c r="BC5" s="314"/>
-      <c r="BD5" s="314"/>
-      <c r="BE5" s="314"/>
-      <c r="BF5" s="314"/>
-      <c r="BG5" s="314"/>
-      <c r="BH5" s="314"/>
-      <c r="BI5" s="314"/>
-      <c r="BJ5" s="314"/>
-      <c r="BK5" s="314"/>
-      <c r="BL5" s="314"/>
-      <c r="BM5" s="314"/>
-      <c r="BN5" s="314"/>
-      <c r="BO5" s="314"/>
-      <c r="BP5" s="315"/>
-      <c r="BQ5" s="268" t="s">
+      <c r="AZ5" s="249"/>
+      <c r="BA5" s="249"/>
+      <c r="BB5" s="249"/>
+      <c r="BC5" s="249"/>
+      <c r="BD5" s="249"/>
+      <c r="BE5" s="249"/>
+      <c r="BF5" s="249"/>
+      <c r="BG5" s="249"/>
+      <c r="BH5" s="249"/>
+      <c r="BI5" s="249"/>
+      <c r="BJ5" s="249"/>
+      <c r="BK5" s="249"/>
+      <c r="BL5" s="249"/>
+      <c r="BM5" s="249"/>
+      <c r="BN5" s="249"/>
+      <c r="BO5" s="249"/>
+      <c r="BP5" s="250"/>
+      <c r="BQ5" s="289" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="275"/>
-      <c r="BS5" s="265" t="s">
+      <c r="BR5" s="294"/>
+      <c r="BS5" s="257" t="s">
         <v>128</v>
       </c>
-      <c r="BT5" s="265" t="s">
+      <c r="BT5" s="257" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="268" t="s">
+      <c r="BU5" s="289" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="250" t="s">
+      <c r="BW5" s="274" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="253" t="s">
+      <c r="BX5" s="277" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="254"/>
-      <c r="BZ5" s="254"/>
-      <c r="CA5" s="255"/>
-      <c r="CB5" s="262" t="s">
+      <c r="BY5" s="278"/>
+      <c r="BZ5" s="278"/>
+      <c r="CA5" s="279"/>
+      <c r="CB5" s="286" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="242" t="s">
+      <c r="CC5" s="271" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="242" t="s">
+      <c r="CD5" s="271" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="142"/>
       <c r="CI5" s="143"/>
     </row>
     <row r="6" spans="1:87" s="141" customFormat="1">
-      <c r="A6" s="300"/>
-      <c r="B6" s="303"/>
+      <c r="A6" s="264"/>
+      <c r="B6" s="267"/>
       <c r="C6" s="246"/>
-      <c r="D6" s="306"/>
-      <c r="E6" s="306"/>
-      <c r="F6" s="341"/>
+      <c r="D6" s="259"/>
+      <c r="E6" s="259"/>
+      <c r="F6" s="320"/>
       <c r="G6" s="246"/>
-      <c r="H6" s="324"/>
-      <c r="I6" s="324"/>
+      <c r="H6" s="298"/>
+      <c r="I6" s="298"/>
       <c r="J6" s="246"/>
-      <c r="K6" s="326" t="s">
+      <c r="K6" s="306" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="326" t="s">
+      <c r="L6" s="306" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="326" t="s">
+      <c r="M6" s="306" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="326" t="s">
+      <c r="N6" s="306" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="326" t="s">
+      <c r="O6" s="306" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="326" t="s">
+      <c r="P6" s="306" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="326" t="s">
+      <c r="Q6" s="306" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="326" t="s">
+      <c r="R6" s="306" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="326" t="s">
+      <c r="S6" s="306" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="326" t="s">
+      <c r="T6" s="306" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="326" t="s">
+      <c r="U6" s="306" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="329" t="s">
+      <c r="V6" s="309" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="330"/>
-      <c r="X6" s="326" t="s">
+      <c r="W6" s="310"/>
+      <c r="X6" s="306" t="s">
         <v>46</v>
       </c>
       <c r="Y6" s="245" t="s">
@@ -18858,31 +19296,31 @@
       <c r="AB6" s="245" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="323" t="s">
+      <c r="AC6" s="297" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="323" t="s">
+      <c r="AD6" s="297" t="s">
         <v>129</v>
       </c>
-      <c r="AE6" s="323" t="s">
+      <c r="AE6" s="297" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="323" t="s">
+      <c r="AF6" s="297" t="s">
         <v>54</v>
       </c>
       <c r="AG6" s="245" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="323" t="s">
+      <c r="AH6" s="297" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="323" t="s">
+      <c r="AI6" s="297" t="s">
         <v>57</v>
       </c>
       <c r="AJ6" s="245" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="320" t="s">
+      <c r="AK6" s="242" t="s">
         <v>59</v>
       </c>
       <c r="AL6" s="245" t="s">
@@ -18891,7 +19329,7 @@
       <c r="AM6" s="245" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="317" t="s">
+      <c r="AN6" s="252" t="s">
         <v>62</v>
       </c>
       <c r="AO6" s="245" t="s">
@@ -18906,90 +19344,90 @@
       <c r="AV6" s="246"/>
       <c r="AW6" s="246"/>
       <c r="AX6" s="246"/>
-      <c r="AY6" s="313" t="s">
+      <c r="AY6" s="248" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="314"/>
-      <c r="BA6" s="314"/>
-      <c r="BB6" s="314"/>
-      <c r="BC6" s="314"/>
-      <c r="BD6" s="314"/>
-      <c r="BE6" s="314"/>
-      <c r="BF6" s="314"/>
-      <c r="BG6" s="314"/>
-      <c r="BH6" s="314"/>
-      <c r="BI6" s="314"/>
-      <c r="BJ6" s="315"/>
-      <c r="BK6" s="313" t="s">
+      <c r="AZ6" s="249"/>
+      <c r="BA6" s="249"/>
+      <c r="BB6" s="249"/>
+      <c r="BC6" s="249"/>
+      <c r="BD6" s="249"/>
+      <c r="BE6" s="249"/>
+      <c r="BF6" s="249"/>
+      <c r="BG6" s="249"/>
+      <c r="BH6" s="249"/>
+      <c r="BI6" s="249"/>
+      <c r="BJ6" s="250"/>
+      <c r="BK6" s="248" t="s">
         <v>65</v>
       </c>
-      <c r="BL6" s="314"/>
-      <c r="BM6" s="314"/>
-      <c r="BN6" s="314"/>
-      <c r="BO6" s="314"/>
-      <c r="BP6" s="315"/>
-      <c r="BQ6" s="266" t="s">
+      <c r="BL6" s="249"/>
+      <c r="BM6" s="249"/>
+      <c r="BN6" s="249"/>
+      <c r="BO6" s="249"/>
+      <c r="BP6" s="250"/>
+      <c r="BQ6" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="BR6" s="266" t="s">
+      <c r="BR6" s="255" t="s">
         <v>67</v>
       </c>
-      <c r="BS6" s="266"/>
-      <c r="BT6" s="266"/>
-      <c r="BU6" s="269"/>
+      <c r="BS6" s="255"/>
+      <c r="BT6" s="255"/>
+      <c r="BU6" s="290"/>
       <c r="BV6"/>
-      <c r="BW6" s="251"/>
-      <c r="BX6" s="256"/>
-      <c r="BY6" s="257"/>
-      <c r="BZ6" s="257"/>
-      <c r="CA6" s="258"/>
-      <c r="CB6" s="263"/>
-      <c r="CC6" s="243"/>
-      <c r="CD6" s="243"/>
+      <c r="BW6" s="275"/>
+      <c r="BX6" s="280"/>
+      <c r="BY6" s="281"/>
+      <c r="BZ6" s="281"/>
+      <c r="CA6" s="282"/>
+      <c r="CB6" s="287"/>
+      <c r="CC6" s="272"/>
+      <c r="CD6" s="272"/>
       <c r="CH6" s="142"/>
       <c r="CI6" s="143"/>
     </row>
     <row r="7" spans="1:87" s="141" customFormat="1">
-      <c r="A7" s="300"/>
-      <c r="B7" s="303"/>
+      <c r="A7" s="264"/>
+      <c r="B7" s="267"/>
       <c r="C7" s="246"/>
-      <c r="D7" s="306"/>
-      <c r="E7" s="306"/>
-      <c r="F7" s="341"/>
+      <c r="D7" s="259"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="320"/>
       <c r="G7" s="246"/>
-      <c r="H7" s="324"/>
-      <c r="I7" s="324"/>
+      <c r="H7" s="298"/>
+      <c r="I7" s="298"/>
       <c r="J7" s="246"/>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
-      <c r="O7" s="327"/>
-      <c r="P7" s="327"/>
-      <c r="Q7" s="327"/>
-      <c r="R7" s="327"/>
-      <c r="S7" s="327"/>
-      <c r="T7" s="327"/>
-      <c r="U7" s="327"/>
-      <c r="V7" s="331"/>
-      <c r="W7" s="332"/>
-      <c r="X7" s="327"/>
+      <c r="K7" s="307"/>
+      <c r="L7" s="307"/>
+      <c r="M7" s="307"/>
+      <c r="N7" s="307"/>
+      <c r="O7" s="307"/>
+      <c r="P7" s="307"/>
+      <c r="Q7" s="307"/>
+      <c r="R7" s="307"/>
+      <c r="S7" s="307"/>
+      <c r="T7" s="307"/>
+      <c r="U7" s="307"/>
+      <c r="V7" s="311"/>
+      <c r="W7" s="312"/>
+      <c r="X7" s="307"/>
       <c r="Y7" s="246"/>
       <c r="Z7" s="246"/>
       <c r="AA7" s="246"/>
       <c r="AB7" s="246"/>
-      <c r="AC7" s="324"/>
-      <c r="AD7" s="324"/>
-      <c r="AE7" s="324"/>
-      <c r="AF7" s="324"/>
+      <c r="AC7" s="298"/>
+      <c r="AD7" s="298"/>
+      <c r="AE7" s="298"/>
+      <c r="AF7" s="298"/>
       <c r="AG7" s="246"/>
-      <c r="AH7" s="324"/>
-      <c r="AI7" s="324"/>
+      <c r="AH7" s="298"/>
+      <c r="AI7" s="298"/>
       <c r="AJ7" s="246"/>
-      <c r="AK7" s="321"/>
+      <c r="AK7" s="243"/>
       <c r="AL7" s="246"/>
       <c r="AM7" s="246"/>
-      <c r="AN7" s="318"/>
+      <c r="AN7" s="253"/>
       <c r="AO7" s="246"/>
       <c r="AP7" s="246"/>
       <c r="AQ7" s="246"/>
@@ -19009,113 +19447,113 @@
       <c r="BA7" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="265" t="s">
+      <c r="BB7" s="257" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="248" t="s">
+      <c r="BC7" s="240" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="248" t="s">
+      <c r="BD7" s="240" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="248" t="s">
+      <c r="BE7" s="240" t="s">
         <v>130</v>
       </c>
-      <c r="BF7" s="248" t="s">
+      <c r="BF7" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="248" t="s">
+      <c r="BG7" s="240" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="248" t="s">
+      <c r="BH7" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="248" t="s">
+      <c r="BI7" s="240" t="s">
         <v>80</v>
       </c>
-      <c r="BJ7" s="311" t="s">
+      <c r="BJ7" s="269" t="s">
         <v>81</v>
       </c>
-      <c r="BK7" s="248" t="s">
+      <c r="BK7" s="240" t="s">
         <v>82</v>
       </c>
-      <c r="BL7" s="265" t="s">
+      <c r="BL7" s="257" t="s">
         <v>83</v>
       </c>
-      <c r="BM7" s="248" t="s">
+      <c r="BM7" s="240" t="s">
         <v>84</v>
       </c>
-      <c r="BN7" s="265" t="s">
+      <c r="BN7" s="257" t="s">
         <v>85</v>
       </c>
-      <c r="BO7" s="265" t="s">
+      <c r="BO7" s="257" t="s">
         <v>131</v>
       </c>
-      <c r="BP7" s="265" t="s">
+      <c r="BP7" s="257" t="s">
         <v>86</v>
       </c>
-      <c r="BQ7" s="266"/>
-      <c r="BR7" s="266"/>
-      <c r="BS7" s="266"/>
-      <c r="BT7" s="266"/>
-      <c r="BU7" s="269"/>
+      <c r="BQ7" s="255"/>
+      <c r="BR7" s="255"/>
+      <c r="BS7" s="255"/>
+      <c r="BT7" s="255"/>
+      <c r="BU7" s="290"/>
       <c r="BV7"/>
-      <c r="BW7" s="252"/>
-      <c r="BX7" s="259"/>
-      <c r="BY7" s="260"/>
-      <c r="BZ7" s="260"/>
-      <c r="CA7" s="261"/>
-      <c r="CB7" s="264"/>
-      <c r="CC7" s="244"/>
-      <c r="CD7" s="244"/>
+      <c r="BW7" s="276"/>
+      <c r="BX7" s="283"/>
+      <c r="BY7" s="284"/>
+      <c r="BZ7" s="284"/>
+      <c r="CA7" s="285"/>
+      <c r="CB7" s="288"/>
+      <c r="CC7" s="273"/>
+      <c r="CD7" s="273"/>
       <c r="CH7" s="142"/>
       <c r="CI7" s="143"/>
     </row>
     <row r="8" spans="1:87" s="141" customFormat="1" ht="24">
-      <c r="A8" s="301"/>
-      <c r="B8" s="304"/>
+      <c r="A8" s="265"/>
+      <c r="B8" s="268"/>
       <c r="C8" s="247"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="307"/>
-      <c r="F8" s="342"/>
+      <c r="D8" s="260"/>
+      <c r="E8" s="260"/>
+      <c r="F8" s="321"/>
       <c r="G8" s="247"/>
-      <c r="H8" s="325"/>
-      <c r="I8" s="325"/>
+      <c r="H8" s="299"/>
+      <c r="I8" s="299"/>
       <c r="J8" s="247"/>
-      <c r="K8" s="328"/>
-      <c r="L8" s="328"/>
-      <c r="M8" s="328"/>
-      <c r="N8" s="328"/>
-      <c r="O8" s="328"/>
-      <c r="P8" s="328"/>
-      <c r="Q8" s="328"/>
-      <c r="R8" s="328"/>
-      <c r="S8" s="328"/>
-      <c r="T8" s="328"/>
-      <c r="U8" s="328"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="308"/>
+      <c r="P8" s="308"/>
+      <c r="Q8" s="308"/>
+      <c r="R8" s="308"/>
+      <c r="S8" s="308"/>
+      <c r="T8" s="308"/>
+      <c r="U8" s="308"/>
       <c r="V8" s="145" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="328"/>
+      <c r="X8" s="308"/>
       <c r="Y8" s="247"/>
       <c r="Z8" s="247"/>
       <c r="AA8" s="247"/>
       <c r="AB8" s="247"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
+      <c r="AC8" s="299"/>
+      <c r="AD8" s="299"/>
+      <c r="AE8" s="299"/>
+      <c r="AF8" s="299"/>
       <c r="AG8" s="247"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
+      <c r="AH8" s="299"/>
+      <c r="AI8" s="299"/>
       <c r="AJ8" s="247"/>
-      <c r="AK8" s="322"/>
+      <c r="AK8" s="244"/>
       <c r="AL8" s="247"/>
       <c r="AM8" s="247"/>
-      <c r="AN8" s="319"/>
+      <c r="AN8" s="254"/>
       <c r="AO8" s="247"/>
       <c r="AP8" s="247"/>
       <c r="AQ8" s="247"/>
@@ -19135,28 +19573,28 @@
       <c r="BA8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="267"/>
-      <c r="BC8" s="249"/>
-      <c r="BD8" s="249"/>
-      <c r="BE8" s="249"/>
-      <c r="BF8" s="249"/>
-      <c r="BG8" s="249"/>
-      <c r="BH8" s="249"/>
-      <c r="BI8" s="249"/>
-      <c r="BJ8" s="312"/>
-      <c r="BK8" s="249"/>
-      <c r="BL8" s="267"/>
-      <c r="BM8" s="249"/>
-      <c r="BN8" s="267"/>
-      <c r="BO8" s="267"/>
-      <c r="BP8" s="267"/>
-      <c r="BQ8" s="267"/>
-      <c r="BR8" s="267"/>
-      <c r="BS8" s="267"/>
-      <c r="BT8" s="267"/>
-      <c r="BU8" s="270"/>
+      <c r="BB8" s="256"/>
+      <c r="BC8" s="241"/>
+      <c r="BD8" s="241"/>
+      <c r="BE8" s="241"/>
+      <c r="BF8" s="241"/>
+      <c r="BG8" s="241"/>
+      <c r="BH8" s="241"/>
+      <c r="BI8" s="241"/>
+      <c r="BJ8" s="270"/>
+      <c r="BK8" s="241"/>
+      <c r="BL8" s="256"/>
+      <c r="BM8" s="241"/>
+      <c r="BN8" s="256"/>
+      <c r="BO8" s="256"/>
+      <c r="BP8" s="256"/>
+      <c r="BQ8" s="256"/>
+      <c r="BR8" s="256"/>
+      <c r="BS8" s="256"/>
+      <c r="BT8" s="256"/>
+      <c r="BU8" s="291"/>
       <c r="BV8"/>
-      <c r="BW8" s="252"/>
+      <c r="BW8" s="276"/>
       <c r="BX8" s="72" t="s">
         <v>92</v>
       </c>
@@ -19169,9 +19607,9 @@
       <c r="CA8" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="264"/>
-      <c r="CC8" s="244"/>
-      <c r="CD8" s="244"/>
+      <c r="CB8" s="288"/>
+      <c r="CC8" s="273"/>
+      <c r="CD8" s="273"/>
       <c r="CF8" s="146"/>
       <c r="CH8" s="142"/>
       <c r="CI8" s="143"/>
@@ -21348,24 +21786,54 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BQ6:BQ8"/>
     <mergeCell ref="BX5:CA7"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="CC5:CC8"/>
@@ -21382,54 +21850,24 @@
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BG7:BG8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BJ7:BJ8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 C9:BU9 B20:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="63"/>
@@ -21442,8 +21880,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
